--- a/template_FtoF_単体テスト仕様書兼成績書_同一集約No.のIF展開時.xlsx
+++ b/template_FtoF_単体テスト仕様書兼成績書_同一集約No.のIF展開時.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="11505" tabRatio="900"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="11505" tabRatio="900" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="表紙 " sheetId="30" r:id="rId1"/>
@@ -1609,33 +1609,6 @@
     <phoneticPr fontId="16"/>
   </si>
   <si>
-    <t>展開元マッピング結果と比較し、
-同じ様にマッピングされることを確認
-■展開元IF：XXXXXX</t>
-    <rPh sb="0" eb="3">
-      <t>テンカイモト</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ヒカク</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="35" eb="38">
-      <t>テンカイモト</t>
-    </rPh>
-    <phoneticPr fontId="16"/>
-  </si>
-  <si>
     <t xml:space="preserve">展開元IFと同じマッピング入力データを使用した場合
 </t>
     <phoneticPr fontId="16"/>
@@ -1671,6 +1644,33 @@
     <t>異常</t>
     <rPh sb="0" eb="2">
       <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>展開元マッピング結果と比較し、
+同じ様にマッピングされることを確認
+■展開元IF：XXXXX</t>
+    <rPh sb="0" eb="3">
+      <t>テンカイモト</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>テンカイモト</t>
     </rPh>
     <phoneticPr fontId="16"/>
   </si>
@@ -19905,6 +19905,72 @@
     <xf numFmtId="0" fontId="81" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="538" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="541" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="549" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="530" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="549" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="541" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="538" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="81" fillId="36" borderId="530" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="36" borderId="538" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="530" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="3" borderId="20" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="3" borderId="0" xfId="151" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="3" borderId="21" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="152" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="89" fillId="3" borderId="20" xfId="151" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="89" fillId="3" borderId="0" xfId="151" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="89" fillId="3" borderId="0" xfId="151" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="89" fillId="3" borderId="21" xfId="151" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="86" fillId="3" borderId="0" xfId="151" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -19932,30 +19998,6 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="48" xfId="152" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="3" borderId="20" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="3" borderId="0" xfId="151" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="3" borderId="21" xfId="151" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="152" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="89" fillId="3" borderId="20" xfId="151" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="89" fillId="3" borderId="0" xfId="151" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="89" fillId="3" borderId="0" xfId="151" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="89" fillId="3" borderId="21" xfId="151" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="198" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -20015,48 +20057,6 @@
     </xf>
     <xf numFmtId="49" fontId="15" fillId="4" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="538" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="541" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="549" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="530" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="549" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="541" xfId="3258" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="538" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="81" fillId="36" borderId="530" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="3258" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="36" borderId="538" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="530" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3300">
@@ -23402,273 +23402,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1270000</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>39687</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="正方形/長方形 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18CF50AB-FF07-42AF-8106-30B8C049FD5F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="533400" y="223837"/>
-          <a:ext cx="4422775" cy="1368425"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>集約</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>No.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>が同じ</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>IF</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>が複数ある場合、どれか一つでマッピングのテストを実施し、その他は入力データとマッピング出力結果に差分がないことを確認するテストのみを実施する</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>例えば、</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>IF</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>①と</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>IF</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>②が同じ集約</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>No.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>の場合、</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>IF</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>①でマッピングテストを行い、</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>IF</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>②では、</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>IF</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>①と同じ入力内容のデータを使って処理を実行し、ＩＦ①と全く同じ結果であることを確認する</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2032000</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>23815</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>2190750</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>39689</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="吹き出し: 四角形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D443763-E302-3C1E-14DE-895BEDB698B3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3251200" y="4052890"/>
-          <a:ext cx="2625725" cy="587374"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val -80626"/>
-            <a:gd name="adj2" fmla="val -109898"/>
-          </a:avLst>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>マッピングテストを実施完了している</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-            <a:t>IF</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>名</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>（比較元となる</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>IF</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>名</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>）</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>を記載</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -24024,703 +23757,703 @@
     </row>
     <row r="3" spans="1:58" ht="14.45" customHeight="1">
       <c r="A3" s="185"/>
-      <c r="C3" s="283" t="s">
+      <c r="C3" s="305" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="283"/>
-      <c r="E3" s="283"/>
-      <c r="F3" s="283"/>
-      <c r="G3" s="283"/>
-      <c r="H3" s="283"/>
-      <c r="I3" s="283"/>
-      <c r="J3" s="283"/>
-      <c r="K3" s="283"/>
-      <c r="L3" s="283"/>
-      <c r="M3" s="283"/>
-      <c r="N3" s="283"/>
-      <c r="O3" s="283"/>
-      <c r="P3" s="283"/>
-      <c r="Q3" s="283"/>
-      <c r="R3" s="283"/>
-      <c r="S3" s="283"/>
-      <c r="T3" s="283"/>
-      <c r="U3" s="283"/>
-      <c r="V3" s="283"/>
-      <c r="W3" s="283"/>
-      <c r="X3" s="283"/>
-      <c r="Y3" s="283"/>
-      <c r="Z3" s="283"/>
-      <c r="AA3" s="283"/>
-      <c r="AB3" s="283"/>
-      <c r="AC3" s="283"/>
-      <c r="AD3" s="283"/>
-      <c r="AE3" s="283"/>
-      <c r="AF3" s="283"/>
-      <c r="AG3" s="283"/>
-      <c r="AH3" s="283"/>
-      <c r="AI3" s="283"/>
-      <c r="AJ3" s="283"/>
-      <c r="AK3" s="283"/>
-      <c r="AL3" s="283"/>
-      <c r="AM3" s="283"/>
-      <c r="AN3" s="283"/>
-      <c r="AO3" s="283"/>
-      <c r="AP3" s="283"/>
-      <c r="AQ3" s="283"/>
-      <c r="AR3" s="283"/>
-      <c r="AS3" s="283"/>
-      <c r="AT3" s="283"/>
-      <c r="AU3" s="283"/>
-      <c r="AV3" s="283"/>
-      <c r="AW3" s="283"/>
-      <c r="AX3" s="283"/>
-      <c r="AY3" s="284"/>
+      <c r="D3" s="305"/>
+      <c r="E3" s="305"/>
+      <c r="F3" s="305"/>
+      <c r="G3" s="305"/>
+      <c r="H3" s="305"/>
+      <c r="I3" s="305"/>
+      <c r="J3" s="305"/>
+      <c r="K3" s="305"/>
+      <c r="L3" s="305"/>
+      <c r="M3" s="305"/>
+      <c r="N3" s="305"/>
+      <c r="O3" s="305"/>
+      <c r="P3" s="305"/>
+      <c r="Q3" s="305"/>
+      <c r="R3" s="305"/>
+      <c r="S3" s="305"/>
+      <c r="T3" s="305"/>
+      <c r="U3" s="305"/>
+      <c r="V3" s="305"/>
+      <c r="W3" s="305"/>
+      <c r="X3" s="305"/>
+      <c r="Y3" s="305"/>
+      <c r="Z3" s="305"/>
+      <c r="AA3" s="305"/>
+      <c r="AB3" s="305"/>
+      <c r="AC3" s="305"/>
+      <c r="AD3" s="305"/>
+      <c r="AE3" s="305"/>
+      <c r="AF3" s="305"/>
+      <c r="AG3" s="305"/>
+      <c r="AH3" s="305"/>
+      <c r="AI3" s="305"/>
+      <c r="AJ3" s="305"/>
+      <c r="AK3" s="305"/>
+      <c r="AL3" s="305"/>
+      <c r="AM3" s="305"/>
+      <c r="AN3" s="305"/>
+      <c r="AO3" s="305"/>
+      <c r="AP3" s="305"/>
+      <c r="AQ3" s="305"/>
+      <c r="AR3" s="305"/>
+      <c r="AS3" s="305"/>
+      <c r="AT3" s="305"/>
+      <c r="AU3" s="305"/>
+      <c r="AV3" s="305"/>
+      <c r="AW3" s="305"/>
+      <c r="AX3" s="305"/>
+      <c r="AY3" s="306"/>
     </row>
     <row r="4" spans="1:58" ht="14.45" customHeight="1">
       <c r="A4" s="185"/>
-      <c r="C4" s="283"/>
-      <c r="D4" s="283"/>
-      <c r="E4" s="283"/>
-      <c r="F4" s="283"/>
-      <c r="G4" s="283"/>
-      <c r="H4" s="283"/>
-      <c r="I4" s="283"/>
-      <c r="J4" s="283"/>
-      <c r="K4" s="283"/>
-      <c r="L4" s="283"/>
-      <c r="M4" s="283"/>
-      <c r="N4" s="283"/>
-      <c r="O4" s="283"/>
-      <c r="P4" s="283"/>
-      <c r="Q4" s="283"/>
-      <c r="R4" s="283"/>
-      <c r="S4" s="283"/>
-      <c r="T4" s="283"/>
-      <c r="U4" s="283"/>
-      <c r="V4" s="283"/>
-      <c r="W4" s="283"/>
-      <c r="X4" s="283"/>
-      <c r="Y4" s="283"/>
-      <c r="Z4" s="283"/>
-      <c r="AA4" s="283"/>
-      <c r="AB4" s="283"/>
-      <c r="AC4" s="283"/>
-      <c r="AD4" s="283"/>
-      <c r="AE4" s="283"/>
-      <c r="AF4" s="283"/>
-      <c r="AG4" s="283"/>
-      <c r="AH4" s="283"/>
-      <c r="AI4" s="283"/>
-      <c r="AJ4" s="283"/>
-      <c r="AK4" s="283"/>
-      <c r="AL4" s="283"/>
-      <c r="AM4" s="283"/>
-      <c r="AN4" s="283"/>
-      <c r="AO4" s="283"/>
-      <c r="AP4" s="283"/>
-      <c r="AQ4" s="283"/>
-      <c r="AR4" s="283"/>
-      <c r="AS4" s="283"/>
-      <c r="AT4" s="283"/>
-      <c r="AU4" s="283"/>
-      <c r="AV4" s="283"/>
-      <c r="AW4" s="283"/>
-      <c r="AX4" s="283"/>
-      <c r="AY4" s="284"/>
+      <c r="C4" s="305"/>
+      <c r="D4" s="305"/>
+      <c r="E4" s="305"/>
+      <c r="F4" s="305"/>
+      <c r="G4" s="305"/>
+      <c r="H4" s="305"/>
+      <c r="I4" s="305"/>
+      <c r="J4" s="305"/>
+      <c r="K4" s="305"/>
+      <c r="L4" s="305"/>
+      <c r="M4" s="305"/>
+      <c r="N4" s="305"/>
+      <c r="O4" s="305"/>
+      <c r="P4" s="305"/>
+      <c r="Q4" s="305"/>
+      <c r="R4" s="305"/>
+      <c r="S4" s="305"/>
+      <c r="T4" s="305"/>
+      <c r="U4" s="305"/>
+      <c r="V4" s="305"/>
+      <c r="W4" s="305"/>
+      <c r="X4" s="305"/>
+      <c r="Y4" s="305"/>
+      <c r="Z4" s="305"/>
+      <c r="AA4" s="305"/>
+      <c r="AB4" s="305"/>
+      <c r="AC4" s="305"/>
+      <c r="AD4" s="305"/>
+      <c r="AE4" s="305"/>
+      <c r="AF4" s="305"/>
+      <c r="AG4" s="305"/>
+      <c r="AH4" s="305"/>
+      <c r="AI4" s="305"/>
+      <c r="AJ4" s="305"/>
+      <c r="AK4" s="305"/>
+      <c r="AL4" s="305"/>
+      <c r="AM4" s="305"/>
+      <c r="AN4" s="305"/>
+      <c r="AO4" s="305"/>
+      <c r="AP4" s="305"/>
+      <c r="AQ4" s="305"/>
+      <c r="AR4" s="305"/>
+      <c r="AS4" s="305"/>
+      <c r="AT4" s="305"/>
+      <c r="AU4" s="305"/>
+      <c r="AV4" s="305"/>
+      <c r="AW4" s="305"/>
+      <c r="AX4" s="305"/>
+      <c r="AY4" s="306"/>
     </row>
     <row r="5" spans="1:58" ht="14.45" customHeight="1">
       <c r="A5" s="185"/>
       <c r="AY5" s="186"/>
     </row>
     <row r="6" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A6" s="285" t="s">
+      <c r="A6" s="307" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="286"/>
-      <c r="C6" s="286"/>
-      <c r="D6" s="286"/>
-      <c r="E6" s="286"/>
-      <c r="F6" s="286"/>
-      <c r="G6" s="286"/>
-      <c r="H6" s="286"/>
-      <c r="I6" s="286"/>
-      <c r="J6" s="286"/>
-      <c r="K6" s="286"/>
-      <c r="L6" s="286"/>
-      <c r="M6" s="286"/>
-      <c r="N6" s="286"/>
-      <c r="O6" s="286"/>
-      <c r="P6" s="286"/>
-      <c r="Q6" s="286"/>
-      <c r="R6" s="286"/>
-      <c r="S6" s="286"/>
-      <c r="T6" s="286"/>
-      <c r="U6" s="286"/>
-      <c r="V6" s="286"/>
-      <c r="W6" s="286"/>
-      <c r="X6" s="286"/>
-      <c r="Y6" s="286"/>
-      <c r="Z6" s="286"/>
-      <c r="AA6" s="286"/>
-      <c r="AB6" s="286"/>
-      <c r="AC6" s="286"/>
-      <c r="AD6" s="286"/>
-      <c r="AE6" s="286"/>
-      <c r="AF6" s="286"/>
-      <c r="AG6" s="286"/>
-      <c r="AH6" s="286"/>
-      <c r="AI6" s="286"/>
-      <c r="AJ6" s="286"/>
-      <c r="AK6" s="286"/>
-      <c r="AL6" s="286"/>
-      <c r="AM6" s="286"/>
-      <c r="AN6" s="286"/>
-      <c r="AO6" s="286"/>
-      <c r="AP6" s="286"/>
-      <c r="AQ6" s="286"/>
-      <c r="AR6" s="286"/>
-      <c r="AS6" s="286"/>
-      <c r="AT6" s="286"/>
-      <c r="AU6" s="286"/>
-      <c r="AV6" s="286"/>
-      <c r="AW6" s="286"/>
-      <c r="AX6" s="286"/>
-      <c r="AY6" s="287"/>
+      <c r="B6" s="308"/>
+      <c r="C6" s="308"/>
+      <c r="D6" s="308"/>
+      <c r="E6" s="308"/>
+      <c r="F6" s="308"/>
+      <c r="G6" s="308"/>
+      <c r="H6" s="308"/>
+      <c r="I6" s="308"/>
+      <c r="J6" s="308"/>
+      <c r="K6" s="308"/>
+      <c r="L6" s="308"/>
+      <c r="M6" s="308"/>
+      <c r="N6" s="308"/>
+      <c r="O6" s="308"/>
+      <c r="P6" s="308"/>
+      <c r="Q6" s="308"/>
+      <c r="R6" s="308"/>
+      <c r="S6" s="308"/>
+      <c r="T6" s="308"/>
+      <c r="U6" s="308"/>
+      <c r="V6" s="308"/>
+      <c r="W6" s="308"/>
+      <c r="X6" s="308"/>
+      <c r="Y6" s="308"/>
+      <c r="Z6" s="308"/>
+      <c r="AA6" s="308"/>
+      <c r="AB6" s="308"/>
+      <c r="AC6" s="308"/>
+      <c r="AD6" s="308"/>
+      <c r="AE6" s="308"/>
+      <c r="AF6" s="308"/>
+      <c r="AG6" s="308"/>
+      <c r="AH6" s="308"/>
+      <c r="AI6" s="308"/>
+      <c r="AJ6" s="308"/>
+      <c r="AK6" s="308"/>
+      <c r="AL6" s="308"/>
+      <c r="AM6" s="308"/>
+      <c r="AN6" s="308"/>
+      <c r="AO6" s="308"/>
+      <c r="AP6" s="308"/>
+      <c r="AQ6" s="308"/>
+      <c r="AR6" s="308"/>
+      <c r="AS6" s="308"/>
+      <c r="AT6" s="308"/>
+      <c r="AU6" s="308"/>
+      <c r="AV6" s="308"/>
+      <c r="AW6" s="308"/>
+      <c r="AX6" s="308"/>
+      <c r="AY6" s="309"/>
     </row>
     <row r="7" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A7" s="285"/>
-      <c r="B7" s="286"/>
-      <c r="C7" s="286"/>
-      <c r="D7" s="286"/>
-      <c r="E7" s="286"/>
-      <c r="F7" s="286"/>
-      <c r="G7" s="286"/>
-      <c r="H7" s="286"/>
-      <c r="I7" s="286"/>
-      <c r="J7" s="286"/>
-      <c r="K7" s="286"/>
-      <c r="L7" s="286"/>
-      <c r="M7" s="286"/>
-      <c r="N7" s="286"/>
-      <c r="O7" s="286"/>
-      <c r="P7" s="286"/>
-      <c r="Q7" s="286"/>
-      <c r="R7" s="286"/>
-      <c r="S7" s="286"/>
-      <c r="T7" s="286"/>
-      <c r="U7" s="286"/>
-      <c r="V7" s="286"/>
-      <c r="W7" s="286"/>
-      <c r="X7" s="286"/>
-      <c r="Y7" s="286"/>
-      <c r="Z7" s="286"/>
-      <c r="AA7" s="286"/>
-      <c r="AB7" s="286"/>
-      <c r="AC7" s="286"/>
-      <c r="AD7" s="286"/>
-      <c r="AE7" s="286"/>
-      <c r="AF7" s="286"/>
-      <c r="AG7" s="286"/>
-      <c r="AH7" s="286"/>
-      <c r="AI7" s="286"/>
-      <c r="AJ7" s="286"/>
-      <c r="AK7" s="286"/>
-      <c r="AL7" s="286"/>
-      <c r="AM7" s="286"/>
-      <c r="AN7" s="286"/>
-      <c r="AO7" s="286"/>
-      <c r="AP7" s="286"/>
-      <c r="AQ7" s="286"/>
-      <c r="AR7" s="286"/>
-      <c r="AS7" s="286"/>
-      <c r="AT7" s="286"/>
-      <c r="AU7" s="286"/>
-      <c r="AV7" s="286"/>
-      <c r="AW7" s="286"/>
-      <c r="AX7" s="286"/>
-      <c r="AY7" s="287"/>
+      <c r="A7" s="307"/>
+      <c r="B7" s="308"/>
+      <c r="C7" s="308"/>
+      <c r="D7" s="308"/>
+      <c r="E7" s="308"/>
+      <c r="F7" s="308"/>
+      <c r="G7" s="308"/>
+      <c r="H7" s="308"/>
+      <c r="I7" s="308"/>
+      <c r="J7" s="308"/>
+      <c r="K7" s="308"/>
+      <c r="L7" s="308"/>
+      <c r="M7" s="308"/>
+      <c r="N7" s="308"/>
+      <c r="O7" s="308"/>
+      <c r="P7" s="308"/>
+      <c r="Q7" s="308"/>
+      <c r="R7" s="308"/>
+      <c r="S7" s="308"/>
+      <c r="T7" s="308"/>
+      <c r="U7" s="308"/>
+      <c r="V7" s="308"/>
+      <c r="W7" s="308"/>
+      <c r="X7" s="308"/>
+      <c r="Y7" s="308"/>
+      <c r="Z7" s="308"/>
+      <c r="AA7" s="308"/>
+      <c r="AB7" s="308"/>
+      <c r="AC7" s="308"/>
+      <c r="AD7" s="308"/>
+      <c r="AE7" s="308"/>
+      <c r="AF7" s="308"/>
+      <c r="AG7" s="308"/>
+      <c r="AH7" s="308"/>
+      <c r="AI7" s="308"/>
+      <c r="AJ7" s="308"/>
+      <c r="AK7" s="308"/>
+      <c r="AL7" s="308"/>
+      <c r="AM7" s="308"/>
+      <c r="AN7" s="308"/>
+      <c r="AO7" s="308"/>
+      <c r="AP7" s="308"/>
+      <c r="AQ7" s="308"/>
+      <c r="AR7" s="308"/>
+      <c r="AS7" s="308"/>
+      <c r="AT7" s="308"/>
+      <c r="AU7" s="308"/>
+      <c r="AV7" s="308"/>
+      <c r="AW7" s="308"/>
+      <c r="AX7" s="308"/>
+      <c r="AY7" s="309"/>
     </row>
     <row r="8" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A8" s="285"/>
-      <c r="B8" s="286"/>
-      <c r="C8" s="286"/>
-      <c r="D8" s="286"/>
-      <c r="E8" s="286"/>
-      <c r="F8" s="286"/>
-      <c r="G8" s="286"/>
-      <c r="H8" s="286"/>
-      <c r="I8" s="286"/>
-      <c r="J8" s="286"/>
-      <c r="K8" s="286"/>
-      <c r="L8" s="286"/>
-      <c r="M8" s="286"/>
-      <c r="N8" s="286"/>
-      <c r="O8" s="286"/>
-      <c r="P8" s="286"/>
-      <c r="Q8" s="286"/>
-      <c r="R8" s="286"/>
-      <c r="S8" s="286"/>
-      <c r="T8" s="286"/>
-      <c r="U8" s="286"/>
-      <c r="V8" s="286"/>
-      <c r="W8" s="286"/>
-      <c r="X8" s="286"/>
-      <c r="Y8" s="286"/>
-      <c r="Z8" s="286"/>
-      <c r="AA8" s="286"/>
-      <c r="AB8" s="286"/>
-      <c r="AC8" s="286"/>
-      <c r="AD8" s="286"/>
-      <c r="AE8" s="286"/>
-      <c r="AF8" s="286"/>
-      <c r="AG8" s="286"/>
-      <c r="AH8" s="286"/>
-      <c r="AI8" s="286"/>
-      <c r="AJ8" s="286"/>
-      <c r="AK8" s="286"/>
-      <c r="AL8" s="286"/>
-      <c r="AM8" s="286"/>
-      <c r="AN8" s="286"/>
-      <c r="AO8" s="286"/>
-      <c r="AP8" s="286"/>
-      <c r="AQ8" s="286"/>
-      <c r="AR8" s="286"/>
-      <c r="AS8" s="286"/>
-      <c r="AT8" s="286"/>
-      <c r="AU8" s="286"/>
-      <c r="AV8" s="286"/>
-      <c r="AW8" s="286"/>
-      <c r="AX8" s="286"/>
-      <c r="AY8" s="287"/>
+      <c r="A8" s="307"/>
+      <c r="B8" s="308"/>
+      <c r="C8" s="308"/>
+      <c r="D8" s="308"/>
+      <c r="E8" s="308"/>
+      <c r="F8" s="308"/>
+      <c r="G8" s="308"/>
+      <c r="H8" s="308"/>
+      <c r="I8" s="308"/>
+      <c r="J8" s="308"/>
+      <c r="K8" s="308"/>
+      <c r="L8" s="308"/>
+      <c r="M8" s="308"/>
+      <c r="N8" s="308"/>
+      <c r="O8" s="308"/>
+      <c r="P8" s="308"/>
+      <c r="Q8" s="308"/>
+      <c r="R8" s="308"/>
+      <c r="S8" s="308"/>
+      <c r="T8" s="308"/>
+      <c r="U8" s="308"/>
+      <c r="V8" s="308"/>
+      <c r="W8" s="308"/>
+      <c r="X8" s="308"/>
+      <c r="Y8" s="308"/>
+      <c r="Z8" s="308"/>
+      <c r="AA8" s="308"/>
+      <c r="AB8" s="308"/>
+      <c r="AC8" s="308"/>
+      <c r="AD8" s="308"/>
+      <c r="AE8" s="308"/>
+      <c r="AF8" s="308"/>
+      <c r="AG8" s="308"/>
+      <c r="AH8" s="308"/>
+      <c r="AI8" s="308"/>
+      <c r="AJ8" s="308"/>
+      <c r="AK8" s="308"/>
+      <c r="AL8" s="308"/>
+      <c r="AM8" s="308"/>
+      <c r="AN8" s="308"/>
+      <c r="AO8" s="308"/>
+      <c r="AP8" s="308"/>
+      <c r="AQ8" s="308"/>
+      <c r="AR8" s="308"/>
+      <c r="AS8" s="308"/>
+      <c r="AT8" s="308"/>
+      <c r="AU8" s="308"/>
+      <c r="AV8" s="308"/>
+      <c r="AW8" s="308"/>
+      <c r="AX8" s="308"/>
+      <c r="AY8" s="309"/>
       <c r="BF8" s="187"/>
     </row>
     <row r="9" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A9" s="285"/>
-      <c r="B9" s="286"/>
-      <c r="C9" s="286"/>
-      <c r="D9" s="286"/>
-      <c r="E9" s="286"/>
-      <c r="F9" s="286"/>
-      <c r="G9" s="286"/>
-      <c r="H9" s="286"/>
-      <c r="I9" s="286"/>
-      <c r="J9" s="286"/>
-      <c r="K9" s="286"/>
-      <c r="L9" s="286"/>
-      <c r="M9" s="286"/>
-      <c r="N9" s="286"/>
-      <c r="O9" s="286"/>
-      <c r="P9" s="286"/>
-      <c r="Q9" s="286"/>
-      <c r="R9" s="286"/>
-      <c r="S9" s="286"/>
-      <c r="T9" s="286"/>
-      <c r="U9" s="286"/>
-      <c r="V9" s="286"/>
-      <c r="W9" s="286"/>
-      <c r="X9" s="286"/>
-      <c r="Y9" s="286"/>
-      <c r="Z9" s="286"/>
-      <c r="AA9" s="286"/>
-      <c r="AB9" s="286"/>
-      <c r="AC9" s="286"/>
-      <c r="AD9" s="286"/>
-      <c r="AE9" s="286"/>
-      <c r="AF9" s="286"/>
-      <c r="AG9" s="286"/>
-      <c r="AH9" s="286"/>
-      <c r="AI9" s="286"/>
-      <c r="AJ9" s="286"/>
-      <c r="AK9" s="286"/>
-      <c r="AL9" s="286"/>
-      <c r="AM9" s="286"/>
-      <c r="AN9" s="286"/>
-      <c r="AO9" s="286"/>
-      <c r="AP9" s="286"/>
-      <c r="AQ9" s="286"/>
-      <c r="AR9" s="286"/>
-      <c r="AS9" s="286"/>
-      <c r="AT9" s="286"/>
-      <c r="AU9" s="286"/>
-      <c r="AV9" s="286"/>
-      <c r="AW9" s="286"/>
-      <c r="AX9" s="286"/>
-      <c r="AY9" s="287"/>
+      <c r="A9" s="307"/>
+      <c r="B9" s="308"/>
+      <c r="C9" s="308"/>
+      <c r="D9" s="308"/>
+      <c r="E9" s="308"/>
+      <c r="F9" s="308"/>
+      <c r="G9" s="308"/>
+      <c r="H9" s="308"/>
+      <c r="I9" s="308"/>
+      <c r="J9" s="308"/>
+      <c r="K9" s="308"/>
+      <c r="L9" s="308"/>
+      <c r="M9" s="308"/>
+      <c r="N9" s="308"/>
+      <c r="O9" s="308"/>
+      <c r="P9" s="308"/>
+      <c r="Q9" s="308"/>
+      <c r="R9" s="308"/>
+      <c r="S9" s="308"/>
+      <c r="T9" s="308"/>
+      <c r="U9" s="308"/>
+      <c r="V9" s="308"/>
+      <c r="W9" s="308"/>
+      <c r="X9" s="308"/>
+      <c r="Y9" s="308"/>
+      <c r="Z9" s="308"/>
+      <c r="AA9" s="308"/>
+      <c r="AB9" s="308"/>
+      <c r="AC9" s="308"/>
+      <c r="AD9" s="308"/>
+      <c r="AE9" s="308"/>
+      <c r="AF9" s="308"/>
+      <c r="AG9" s="308"/>
+      <c r="AH9" s="308"/>
+      <c r="AI9" s="308"/>
+      <c r="AJ9" s="308"/>
+      <c r="AK9" s="308"/>
+      <c r="AL9" s="308"/>
+      <c r="AM9" s="308"/>
+      <c r="AN9" s="308"/>
+      <c r="AO9" s="308"/>
+      <c r="AP9" s="308"/>
+      <c r="AQ9" s="308"/>
+      <c r="AR9" s="308"/>
+      <c r="AS9" s="308"/>
+      <c r="AT9" s="308"/>
+      <c r="AU9" s="308"/>
+      <c r="AV9" s="308"/>
+      <c r="AW9" s="308"/>
+      <c r="AX9" s="308"/>
+      <c r="AY9" s="309"/>
     </row>
     <row r="10" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A10" s="285"/>
-      <c r="B10" s="286"/>
-      <c r="C10" s="286"/>
-      <c r="D10" s="286"/>
-      <c r="E10" s="286"/>
-      <c r="F10" s="286"/>
-      <c r="G10" s="286"/>
-      <c r="H10" s="286"/>
-      <c r="I10" s="286"/>
-      <c r="J10" s="286"/>
-      <c r="K10" s="286"/>
-      <c r="L10" s="286"/>
-      <c r="M10" s="286"/>
-      <c r="N10" s="286"/>
-      <c r="O10" s="286"/>
-      <c r="P10" s="286"/>
-      <c r="Q10" s="286"/>
-      <c r="R10" s="286"/>
-      <c r="S10" s="286"/>
-      <c r="T10" s="286"/>
-      <c r="U10" s="286"/>
-      <c r="V10" s="286"/>
-      <c r="W10" s="286"/>
-      <c r="X10" s="286"/>
-      <c r="Y10" s="286"/>
-      <c r="Z10" s="286"/>
-      <c r="AA10" s="286"/>
-      <c r="AB10" s="286"/>
-      <c r="AC10" s="286"/>
-      <c r="AD10" s="286"/>
-      <c r="AE10" s="286"/>
-      <c r="AF10" s="286"/>
-      <c r="AG10" s="286"/>
-      <c r="AH10" s="286"/>
-      <c r="AI10" s="286"/>
-      <c r="AJ10" s="286"/>
-      <c r="AK10" s="286"/>
-      <c r="AL10" s="286"/>
-      <c r="AM10" s="286"/>
-      <c r="AN10" s="286"/>
-      <c r="AO10" s="286"/>
-      <c r="AP10" s="286"/>
-      <c r="AQ10" s="286"/>
-      <c r="AR10" s="286"/>
-      <c r="AS10" s="286"/>
-      <c r="AT10" s="286"/>
-      <c r="AU10" s="286"/>
-      <c r="AV10" s="286"/>
-      <c r="AW10" s="286"/>
-      <c r="AX10" s="286"/>
-      <c r="AY10" s="287"/>
+      <c r="A10" s="307"/>
+      <c r="B10" s="308"/>
+      <c r="C10" s="308"/>
+      <c r="D10" s="308"/>
+      <c r="E10" s="308"/>
+      <c r="F10" s="308"/>
+      <c r="G10" s="308"/>
+      <c r="H10" s="308"/>
+      <c r="I10" s="308"/>
+      <c r="J10" s="308"/>
+      <c r="K10" s="308"/>
+      <c r="L10" s="308"/>
+      <c r="M10" s="308"/>
+      <c r="N10" s="308"/>
+      <c r="O10" s="308"/>
+      <c r="P10" s="308"/>
+      <c r="Q10" s="308"/>
+      <c r="R10" s="308"/>
+      <c r="S10" s="308"/>
+      <c r="T10" s="308"/>
+      <c r="U10" s="308"/>
+      <c r="V10" s="308"/>
+      <c r="W10" s="308"/>
+      <c r="X10" s="308"/>
+      <c r="Y10" s="308"/>
+      <c r="Z10" s="308"/>
+      <c r="AA10" s="308"/>
+      <c r="AB10" s="308"/>
+      <c r="AC10" s="308"/>
+      <c r="AD10" s="308"/>
+      <c r="AE10" s="308"/>
+      <c r="AF10" s="308"/>
+      <c r="AG10" s="308"/>
+      <c r="AH10" s="308"/>
+      <c r="AI10" s="308"/>
+      <c r="AJ10" s="308"/>
+      <c r="AK10" s="308"/>
+      <c r="AL10" s="308"/>
+      <c r="AM10" s="308"/>
+      <c r="AN10" s="308"/>
+      <c r="AO10" s="308"/>
+      <c r="AP10" s="308"/>
+      <c r="AQ10" s="308"/>
+      <c r="AR10" s="308"/>
+      <c r="AS10" s="308"/>
+      <c r="AT10" s="308"/>
+      <c r="AU10" s="308"/>
+      <c r="AV10" s="308"/>
+      <c r="AW10" s="308"/>
+      <c r="AX10" s="308"/>
+      <c r="AY10" s="309"/>
     </row>
     <row r="11" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A11" s="288" t="s">
+      <c r="A11" s="310" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="289"/>
-      <c r="C11" s="289"/>
-      <c r="D11" s="289"/>
-      <c r="E11" s="289"/>
-      <c r="F11" s="289"/>
-      <c r="G11" s="289"/>
-      <c r="H11" s="289"/>
-      <c r="I11" s="289"/>
-      <c r="J11" s="289"/>
-      <c r="K11" s="289"/>
-      <c r="L11" s="289"/>
-      <c r="M11" s="289"/>
-      <c r="N11" s="289"/>
-      <c r="O11" s="289"/>
-      <c r="P11" s="289"/>
-      <c r="Q11" s="289"/>
-      <c r="R11" s="289"/>
-      <c r="S11" s="289"/>
-      <c r="T11" s="289"/>
-      <c r="U11" s="289"/>
-      <c r="V11" s="289"/>
-      <c r="W11" s="289"/>
-      <c r="X11" s="289"/>
-      <c r="Y11" s="289"/>
-      <c r="Z11" s="289"/>
-      <c r="AA11" s="289"/>
-      <c r="AB11" s="289"/>
-      <c r="AC11" s="289"/>
-      <c r="AD11" s="289"/>
-      <c r="AE11" s="289"/>
-      <c r="AF11" s="289"/>
-      <c r="AG11" s="289"/>
-      <c r="AH11" s="289"/>
-      <c r="AI11" s="289"/>
-      <c r="AJ11" s="289"/>
-      <c r="AK11" s="289"/>
-      <c r="AL11" s="289"/>
-      <c r="AM11" s="289"/>
-      <c r="AN11" s="289"/>
-      <c r="AO11" s="289"/>
-      <c r="AP11" s="289"/>
-      <c r="AQ11" s="289"/>
-      <c r="AR11" s="289"/>
-      <c r="AS11" s="289"/>
-      <c r="AT11" s="289"/>
-      <c r="AU11" s="289"/>
-      <c r="AV11" s="289"/>
-      <c r="AW11" s="289"/>
-      <c r="AX11" s="289"/>
-      <c r="AY11" s="290"/>
+      <c r="B11" s="311"/>
+      <c r="C11" s="311"/>
+      <c r="D11" s="311"/>
+      <c r="E11" s="311"/>
+      <c r="F11" s="311"/>
+      <c r="G11" s="311"/>
+      <c r="H11" s="311"/>
+      <c r="I11" s="311"/>
+      <c r="J11" s="311"/>
+      <c r="K11" s="311"/>
+      <c r="L11" s="311"/>
+      <c r="M11" s="311"/>
+      <c r="N11" s="311"/>
+      <c r="O11" s="311"/>
+      <c r="P11" s="311"/>
+      <c r="Q11" s="311"/>
+      <c r="R11" s="311"/>
+      <c r="S11" s="311"/>
+      <c r="T11" s="311"/>
+      <c r="U11" s="311"/>
+      <c r="V11" s="311"/>
+      <c r="W11" s="311"/>
+      <c r="X11" s="311"/>
+      <c r="Y11" s="311"/>
+      <c r="Z11" s="311"/>
+      <c r="AA11" s="311"/>
+      <c r="AB11" s="311"/>
+      <c r="AC11" s="311"/>
+      <c r="AD11" s="311"/>
+      <c r="AE11" s="311"/>
+      <c r="AF11" s="311"/>
+      <c r="AG11" s="311"/>
+      <c r="AH11" s="311"/>
+      <c r="AI11" s="311"/>
+      <c r="AJ11" s="311"/>
+      <c r="AK11" s="311"/>
+      <c r="AL11" s="311"/>
+      <c r="AM11" s="311"/>
+      <c r="AN11" s="311"/>
+      <c r="AO11" s="311"/>
+      <c r="AP11" s="311"/>
+      <c r="AQ11" s="311"/>
+      <c r="AR11" s="311"/>
+      <c r="AS11" s="311"/>
+      <c r="AT11" s="311"/>
+      <c r="AU11" s="311"/>
+      <c r="AV11" s="311"/>
+      <c r="AW11" s="311"/>
+      <c r="AX11" s="311"/>
+      <c r="AY11" s="312"/>
     </row>
     <row r="12" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A12" s="288"/>
-      <c r="B12" s="289"/>
-      <c r="C12" s="289"/>
-      <c r="D12" s="289"/>
-      <c r="E12" s="289"/>
-      <c r="F12" s="289"/>
-      <c r="G12" s="289"/>
-      <c r="H12" s="289"/>
-      <c r="I12" s="289"/>
-      <c r="J12" s="289"/>
-      <c r="K12" s="289"/>
-      <c r="L12" s="289"/>
-      <c r="M12" s="289"/>
-      <c r="N12" s="289"/>
-      <c r="O12" s="289"/>
-      <c r="P12" s="289"/>
-      <c r="Q12" s="289"/>
-      <c r="R12" s="289"/>
-      <c r="S12" s="289"/>
-      <c r="T12" s="289"/>
-      <c r="U12" s="289"/>
-      <c r="V12" s="289"/>
-      <c r="W12" s="289"/>
-      <c r="X12" s="289"/>
-      <c r="Y12" s="289"/>
-      <c r="Z12" s="289"/>
-      <c r="AA12" s="289"/>
-      <c r="AB12" s="289"/>
-      <c r="AC12" s="289"/>
-      <c r="AD12" s="289"/>
-      <c r="AE12" s="289"/>
-      <c r="AF12" s="289"/>
-      <c r="AG12" s="289"/>
-      <c r="AH12" s="289"/>
-      <c r="AI12" s="289"/>
-      <c r="AJ12" s="289"/>
-      <c r="AK12" s="289"/>
-      <c r="AL12" s="289"/>
-      <c r="AM12" s="289"/>
-      <c r="AN12" s="289"/>
-      <c r="AO12" s="289"/>
-      <c r="AP12" s="289"/>
-      <c r="AQ12" s="289"/>
-      <c r="AR12" s="289"/>
-      <c r="AS12" s="289"/>
-      <c r="AT12" s="289"/>
-      <c r="AU12" s="289"/>
-      <c r="AV12" s="289"/>
-      <c r="AW12" s="289"/>
-      <c r="AX12" s="289"/>
-      <c r="AY12" s="290"/>
+      <c r="A12" s="310"/>
+      <c r="B12" s="311"/>
+      <c r="C12" s="311"/>
+      <c r="D12" s="311"/>
+      <c r="E12" s="311"/>
+      <c r="F12" s="311"/>
+      <c r="G12" s="311"/>
+      <c r="H12" s="311"/>
+      <c r="I12" s="311"/>
+      <c r="J12" s="311"/>
+      <c r="K12" s="311"/>
+      <c r="L12" s="311"/>
+      <c r="M12" s="311"/>
+      <c r="N12" s="311"/>
+      <c r="O12" s="311"/>
+      <c r="P12" s="311"/>
+      <c r="Q12" s="311"/>
+      <c r="R12" s="311"/>
+      <c r="S12" s="311"/>
+      <c r="T12" s="311"/>
+      <c r="U12" s="311"/>
+      <c r="V12" s="311"/>
+      <c r="W12" s="311"/>
+      <c r="X12" s="311"/>
+      <c r="Y12" s="311"/>
+      <c r="Z12" s="311"/>
+      <c r="AA12" s="311"/>
+      <c r="AB12" s="311"/>
+      <c r="AC12" s="311"/>
+      <c r="AD12" s="311"/>
+      <c r="AE12" s="311"/>
+      <c r="AF12" s="311"/>
+      <c r="AG12" s="311"/>
+      <c r="AH12" s="311"/>
+      <c r="AI12" s="311"/>
+      <c r="AJ12" s="311"/>
+      <c r="AK12" s="311"/>
+      <c r="AL12" s="311"/>
+      <c r="AM12" s="311"/>
+      <c r="AN12" s="311"/>
+      <c r="AO12" s="311"/>
+      <c r="AP12" s="311"/>
+      <c r="AQ12" s="311"/>
+      <c r="AR12" s="311"/>
+      <c r="AS12" s="311"/>
+      <c r="AT12" s="311"/>
+      <c r="AU12" s="311"/>
+      <c r="AV12" s="311"/>
+      <c r="AW12" s="311"/>
+      <c r="AX12" s="311"/>
+      <c r="AY12" s="312"/>
     </row>
     <row r="13" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A13" s="288"/>
-      <c r="B13" s="289"/>
-      <c r="C13" s="289"/>
-      <c r="D13" s="289"/>
-      <c r="E13" s="289"/>
-      <c r="F13" s="289"/>
-      <c r="G13" s="289"/>
-      <c r="H13" s="289"/>
-      <c r="I13" s="289"/>
-      <c r="J13" s="289"/>
-      <c r="K13" s="289"/>
-      <c r="L13" s="289"/>
-      <c r="M13" s="289"/>
-      <c r="N13" s="289"/>
-      <c r="O13" s="289"/>
-      <c r="P13" s="289"/>
-      <c r="Q13" s="289"/>
-      <c r="R13" s="289"/>
-      <c r="S13" s="289"/>
-      <c r="T13" s="289"/>
-      <c r="U13" s="289"/>
-      <c r="V13" s="289"/>
-      <c r="W13" s="289"/>
-      <c r="X13" s="289"/>
-      <c r="Y13" s="289"/>
-      <c r="Z13" s="289"/>
-      <c r="AA13" s="289"/>
-      <c r="AB13" s="289"/>
-      <c r="AC13" s="289"/>
-      <c r="AD13" s="289"/>
-      <c r="AE13" s="289"/>
-      <c r="AF13" s="289"/>
-      <c r="AG13" s="289"/>
-      <c r="AH13" s="289"/>
-      <c r="AI13" s="289"/>
-      <c r="AJ13" s="289"/>
-      <c r="AK13" s="289"/>
-      <c r="AL13" s="289"/>
-      <c r="AM13" s="289"/>
-      <c r="AN13" s="289"/>
-      <c r="AO13" s="289"/>
-      <c r="AP13" s="289"/>
-      <c r="AQ13" s="289"/>
-      <c r="AR13" s="289"/>
-      <c r="AS13" s="289"/>
-      <c r="AT13" s="289"/>
-      <c r="AU13" s="289"/>
-      <c r="AV13" s="289"/>
-      <c r="AW13" s="289"/>
-      <c r="AX13" s="289"/>
-      <c r="AY13" s="290"/>
+      <c r="A13" s="310"/>
+      <c r="B13" s="311"/>
+      <c r="C13" s="311"/>
+      <c r="D13" s="311"/>
+      <c r="E13" s="311"/>
+      <c r="F13" s="311"/>
+      <c r="G13" s="311"/>
+      <c r="H13" s="311"/>
+      <c r="I13" s="311"/>
+      <c r="J13" s="311"/>
+      <c r="K13" s="311"/>
+      <c r="L13" s="311"/>
+      <c r="M13" s="311"/>
+      <c r="N13" s="311"/>
+      <c r="O13" s="311"/>
+      <c r="P13" s="311"/>
+      <c r="Q13" s="311"/>
+      <c r="R13" s="311"/>
+      <c r="S13" s="311"/>
+      <c r="T13" s="311"/>
+      <c r="U13" s="311"/>
+      <c r="V13" s="311"/>
+      <c r="W13" s="311"/>
+      <c r="X13" s="311"/>
+      <c r="Y13" s="311"/>
+      <c r="Z13" s="311"/>
+      <c r="AA13" s="311"/>
+      <c r="AB13" s="311"/>
+      <c r="AC13" s="311"/>
+      <c r="AD13" s="311"/>
+      <c r="AE13" s="311"/>
+      <c r="AF13" s="311"/>
+      <c r="AG13" s="311"/>
+      <c r="AH13" s="311"/>
+      <c r="AI13" s="311"/>
+      <c r="AJ13" s="311"/>
+      <c r="AK13" s="311"/>
+      <c r="AL13" s="311"/>
+      <c r="AM13" s="311"/>
+      <c r="AN13" s="311"/>
+      <c r="AO13" s="311"/>
+      <c r="AP13" s="311"/>
+      <c r="AQ13" s="311"/>
+      <c r="AR13" s="311"/>
+      <c r="AS13" s="311"/>
+      <c r="AT13" s="311"/>
+      <c r="AU13" s="311"/>
+      <c r="AV13" s="311"/>
+      <c r="AW13" s="311"/>
+      <c r="AX13" s="311"/>
+      <c r="AY13" s="312"/>
     </row>
     <row r="14" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A14" s="285" t="s">
+      <c r="A14" s="307" t="s">
         <v>126</v>
       </c>
-      <c r="B14" s="289"/>
-      <c r="C14" s="289"/>
-      <c r="D14" s="289"/>
-      <c r="E14" s="289"/>
-      <c r="F14" s="289"/>
-      <c r="G14" s="289"/>
-      <c r="H14" s="289"/>
-      <c r="I14" s="289"/>
-      <c r="J14" s="289"/>
-      <c r="K14" s="289"/>
-      <c r="L14" s="289"/>
-      <c r="M14" s="289"/>
-      <c r="N14" s="289"/>
-      <c r="O14" s="289"/>
-      <c r="P14" s="289"/>
-      <c r="Q14" s="289"/>
-      <c r="R14" s="289"/>
-      <c r="S14" s="289"/>
-      <c r="T14" s="289"/>
-      <c r="U14" s="289"/>
-      <c r="V14" s="289"/>
-      <c r="W14" s="289"/>
-      <c r="X14" s="289"/>
-      <c r="Y14" s="289"/>
-      <c r="Z14" s="289"/>
-      <c r="AA14" s="289"/>
-      <c r="AB14" s="289"/>
-      <c r="AC14" s="289"/>
-      <c r="AD14" s="289"/>
-      <c r="AE14" s="289"/>
-      <c r="AF14" s="289"/>
-      <c r="AG14" s="289"/>
-      <c r="AH14" s="289"/>
-      <c r="AI14" s="289"/>
-      <c r="AJ14" s="289"/>
-      <c r="AK14" s="289"/>
-      <c r="AL14" s="289"/>
-      <c r="AM14" s="289"/>
-      <c r="AN14" s="289"/>
-      <c r="AO14" s="289"/>
-      <c r="AP14" s="289"/>
-      <c r="AQ14" s="289"/>
-      <c r="AR14" s="289"/>
-      <c r="AS14" s="289"/>
-      <c r="AT14" s="289"/>
-      <c r="AU14" s="289"/>
-      <c r="AV14" s="289"/>
-      <c r="AW14" s="289"/>
-      <c r="AX14" s="289"/>
-      <c r="AY14" s="290"/>
+      <c r="B14" s="311"/>
+      <c r="C14" s="311"/>
+      <c r="D14" s="311"/>
+      <c r="E14" s="311"/>
+      <c r="F14" s="311"/>
+      <c r="G14" s="311"/>
+      <c r="H14" s="311"/>
+      <c r="I14" s="311"/>
+      <c r="J14" s="311"/>
+      <c r="K14" s="311"/>
+      <c r="L14" s="311"/>
+      <c r="M14" s="311"/>
+      <c r="N14" s="311"/>
+      <c r="O14" s="311"/>
+      <c r="P14" s="311"/>
+      <c r="Q14" s="311"/>
+      <c r="R14" s="311"/>
+      <c r="S14" s="311"/>
+      <c r="T14" s="311"/>
+      <c r="U14" s="311"/>
+      <c r="V14" s="311"/>
+      <c r="W14" s="311"/>
+      <c r="X14" s="311"/>
+      <c r="Y14" s="311"/>
+      <c r="Z14" s="311"/>
+      <c r="AA14" s="311"/>
+      <c r="AB14" s="311"/>
+      <c r="AC14" s="311"/>
+      <c r="AD14" s="311"/>
+      <c r="AE14" s="311"/>
+      <c r="AF14" s="311"/>
+      <c r="AG14" s="311"/>
+      <c r="AH14" s="311"/>
+      <c r="AI14" s="311"/>
+      <c r="AJ14" s="311"/>
+      <c r="AK14" s="311"/>
+      <c r="AL14" s="311"/>
+      <c r="AM14" s="311"/>
+      <c r="AN14" s="311"/>
+      <c r="AO14" s="311"/>
+      <c r="AP14" s="311"/>
+      <c r="AQ14" s="311"/>
+      <c r="AR14" s="311"/>
+      <c r="AS14" s="311"/>
+      <c r="AT14" s="311"/>
+      <c r="AU14" s="311"/>
+      <c r="AV14" s="311"/>
+      <c r="AW14" s="311"/>
+      <c r="AX14" s="311"/>
+      <c r="AY14" s="312"/>
     </row>
     <row r="15" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A15" s="288"/>
-      <c r="B15" s="289"/>
-      <c r="C15" s="289"/>
-      <c r="D15" s="289"/>
-      <c r="E15" s="289"/>
-      <c r="F15" s="289"/>
-      <c r="G15" s="289"/>
-      <c r="H15" s="289"/>
-      <c r="I15" s="289"/>
-      <c r="J15" s="289"/>
-      <c r="K15" s="289"/>
-      <c r="L15" s="289"/>
-      <c r="M15" s="289"/>
-      <c r="N15" s="289"/>
-      <c r="O15" s="289"/>
-      <c r="P15" s="289"/>
-      <c r="Q15" s="289"/>
-      <c r="R15" s="289"/>
-      <c r="S15" s="289"/>
-      <c r="T15" s="289"/>
-      <c r="U15" s="289"/>
-      <c r="V15" s="289"/>
-      <c r="W15" s="289"/>
-      <c r="X15" s="289"/>
-      <c r="Y15" s="289"/>
-      <c r="Z15" s="289"/>
-      <c r="AA15" s="289"/>
-      <c r="AB15" s="289"/>
-      <c r="AC15" s="289"/>
-      <c r="AD15" s="289"/>
-      <c r="AE15" s="289"/>
-      <c r="AF15" s="289"/>
-      <c r="AG15" s="289"/>
-      <c r="AH15" s="289"/>
-      <c r="AI15" s="289"/>
-      <c r="AJ15" s="289"/>
-      <c r="AK15" s="289"/>
-      <c r="AL15" s="289"/>
-      <c r="AM15" s="289"/>
-      <c r="AN15" s="289"/>
-      <c r="AO15" s="289"/>
-      <c r="AP15" s="289"/>
-      <c r="AQ15" s="289"/>
-      <c r="AR15" s="289"/>
-      <c r="AS15" s="289"/>
-      <c r="AT15" s="289"/>
-      <c r="AU15" s="289"/>
-      <c r="AV15" s="289"/>
-      <c r="AW15" s="289"/>
-      <c r="AX15" s="289"/>
-      <c r="AY15" s="290"/>
+      <c r="A15" s="310"/>
+      <c r="B15" s="311"/>
+      <c r="C15" s="311"/>
+      <c r="D15" s="311"/>
+      <c r="E15" s="311"/>
+      <c r="F15" s="311"/>
+      <c r="G15" s="311"/>
+      <c r="H15" s="311"/>
+      <c r="I15" s="311"/>
+      <c r="J15" s="311"/>
+      <c r="K15" s="311"/>
+      <c r="L15" s="311"/>
+      <c r="M15" s="311"/>
+      <c r="N15" s="311"/>
+      <c r="O15" s="311"/>
+      <c r="P15" s="311"/>
+      <c r="Q15" s="311"/>
+      <c r="R15" s="311"/>
+      <c r="S15" s="311"/>
+      <c r="T15" s="311"/>
+      <c r="U15" s="311"/>
+      <c r="V15" s="311"/>
+      <c r="W15" s="311"/>
+      <c r="X15" s="311"/>
+      <c r="Y15" s="311"/>
+      <c r="Z15" s="311"/>
+      <c r="AA15" s="311"/>
+      <c r="AB15" s="311"/>
+      <c r="AC15" s="311"/>
+      <c r="AD15" s="311"/>
+      <c r="AE15" s="311"/>
+      <c r="AF15" s="311"/>
+      <c r="AG15" s="311"/>
+      <c r="AH15" s="311"/>
+      <c r="AI15" s="311"/>
+      <c r="AJ15" s="311"/>
+      <c r="AK15" s="311"/>
+      <c r="AL15" s="311"/>
+      <c r="AM15" s="311"/>
+      <c r="AN15" s="311"/>
+      <c r="AO15" s="311"/>
+      <c r="AP15" s="311"/>
+      <c r="AQ15" s="311"/>
+      <c r="AR15" s="311"/>
+      <c r="AS15" s="311"/>
+      <c r="AT15" s="311"/>
+      <c r="AU15" s="311"/>
+      <c r="AV15" s="311"/>
+      <c r="AW15" s="311"/>
+      <c r="AX15" s="311"/>
+      <c r="AY15" s="312"/>
     </row>
     <row r="16" spans="1:58" ht="14.45" customHeight="1">
-      <c r="A16" s="288"/>
-      <c r="B16" s="289"/>
-      <c r="C16" s="289"/>
-      <c r="D16" s="289"/>
-      <c r="E16" s="289"/>
-      <c r="F16" s="289"/>
-      <c r="G16" s="289"/>
-      <c r="H16" s="289"/>
-      <c r="I16" s="289"/>
-      <c r="J16" s="289"/>
-      <c r="K16" s="289"/>
-      <c r="L16" s="289"/>
-      <c r="M16" s="289"/>
-      <c r="N16" s="289"/>
-      <c r="O16" s="289"/>
-      <c r="P16" s="289"/>
-      <c r="Q16" s="289"/>
-      <c r="R16" s="289"/>
-      <c r="S16" s="289"/>
-      <c r="T16" s="289"/>
-      <c r="U16" s="289"/>
-      <c r="V16" s="289"/>
-      <c r="W16" s="289"/>
-      <c r="X16" s="289"/>
-      <c r="Y16" s="289"/>
-      <c r="Z16" s="289"/>
-      <c r="AA16" s="289"/>
-      <c r="AB16" s="289"/>
-      <c r="AC16" s="289"/>
-      <c r="AD16" s="289"/>
-      <c r="AE16" s="289"/>
-      <c r="AF16" s="289"/>
-      <c r="AG16" s="289"/>
-      <c r="AH16" s="289"/>
-      <c r="AI16" s="289"/>
-      <c r="AJ16" s="289"/>
-      <c r="AK16" s="289"/>
-      <c r="AL16" s="289"/>
-      <c r="AM16" s="289"/>
-      <c r="AN16" s="289"/>
-      <c r="AO16" s="289"/>
-      <c r="AP16" s="289"/>
-      <c r="AQ16" s="289"/>
-      <c r="AR16" s="289"/>
-      <c r="AS16" s="289"/>
-      <c r="AT16" s="289"/>
-      <c r="AU16" s="289"/>
-      <c r="AV16" s="289"/>
-      <c r="AW16" s="289"/>
-      <c r="AX16" s="289"/>
-      <c r="AY16" s="290"/>
+      <c r="A16" s="310"/>
+      <c r="B16" s="311"/>
+      <c r="C16" s="311"/>
+      <c r="D16" s="311"/>
+      <c r="E16" s="311"/>
+      <c r="F16" s="311"/>
+      <c r="G16" s="311"/>
+      <c r="H16" s="311"/>
+      <c r="I16" s="311"/>
+      <c r="J16" s="311"/>
+      <c r="K16" s="311"/>
+      <c r="L16" s="311"/>
+      <c r="M16" s="311"/>
+      <c r="N16" s="311"/>
+      <c r="O16" s="311"/>
+      <c r="P16" s="311"/>
+      <c r="Q16" s="311"/>
+      <c r="R16" s="311"/>
+      <c r="S16" s="311"/>
+      <c r="T16" s="311"/>
+      <c r="U16" s="311"/>
+      <c r="V16" s="311"/>
+      <c r="W16" s="311"/>
+      <c r="X16" s="311"/>
+      <c r="Y16" s="311"/>
+      <c r="Z16" s="311"/>
+      <c r="AA16" s="311"/>
+      <c r="AB16" s="311"/>
+      <c r="AC16" s="311"/>
+      <c r="AD16" s="311"/>
+      <c r="AE16" s="311"/>
+      <c r="AF16" s="311"/>
+      <c r="AG16" s="311"/>
+      <c r="AH16" s="311"/>
+      <c r="AI16" s="311"/>
+      <c r="AJ16" s="311"/>
+      <c r="AK16" s="311"/>
+      <c r="AL16" s="311"/>
+      <c r="AM16" s="311"/>
+      <c r="AN16" s="311"/>
+      <c r="AO16" s="311"/>
+      <c r="AP16" s="311"/>
+      <c r="AQ16" s="311"/>
+      <c r="AR16" s="311"/>
+      <c r="AS16" s="311"/>
+      <c r="AT16" s="311"/>
+      <c r="AU16" s="311"/>
+      <c r="AV16" s="311"/>
+      <c r="AW16" s="311"/>
+      <c r="AX16" s="311"/>
+      <c r="AY16" s="312"/>
     </row>
     <row r="17" spans="1:51" ht="14.45" customHeight="1">
       <c r="A17" s="185"/>
@@ -24728,122 +24461,122 @@
     </row>
     <row r="18" spans="1:51" ht="14.45" customHeight="1">
       <c r="A18" s="185"/>
-      <c r="Q18" s="291"/>
-      <c r="R18" s="291"/>
-      <c r="S18" s="291"/>
-      <c r="T18" s="291"/>
-      <c r="U18" s="291"/>
-      <c r="V18" s="291"/>
-      <c r="W18" s="291"/>
-      <c r="X18" s="291"/>
-      <c r="Y18" s="291"/>
-      <c r="Z18" s="291"/>
-      <c r="AA18" s="291"/>
-      <c r="AB18" s="291"/>
-      <c r="AC18" s="291"/>
-      <c r="AD18" s="291"/>
-      <c r="AE18" s="291"/>
-      <c r="AF18" s="291"/>
-      <c r="AG18" s="291"/>
-      <c r="AH18" s="291"/>
-      <c r="AI18" s="291"/>
-      <c r="AJ18" s="291"/>
+      <c r="Q18" s="313"/>
+      <c r="R18" s="313"/>
+      <c r="S18" s="313"/>
+      <c r="T18" s="313"/>
+      <c r="U18" s="313"/>
+      <c r="V18" s="313"/>
+      <c r="W18" s="313"/>
+      <c r="X18" s="313"/>
+      <c r="Y18" s="313"/>
+      <c r="Z18" s="313"/>
+      <c r="AA18" s="313"/>
+      <c r="AB18" s="313"/>
+      <c r="AC18" s="313"/>
+      <c r="AD18" s="313"/>
+      <c r="AE18" s="313"/>
+      <c r="AF18" s="313"/>
+      <c r="AG18" s="313"/>
+      <c r="AH18" s="313"/>
+      <c r="AI18" s="313"/>
+      <c r="AJ18" s="313"/>
       <c r="AY18" s="186"/>
     </row>
     <row r="19" spans="1:51" ht="14.45" customHeight="1">
       <c r="A19" s="185"/>
-      <c r="Q19" s="295"/>
-      <c r="R19" s="295"/>
-      <c r="S19" s="295"/>
-      <c r="T19" s="295"/>
-      <c r="U19" s="295"/>
-      <c r="V19" s="295"/>
-      <c r="W19" s="295"/>
-      <c r="X19" s="295"/>
-      <c r="Y19" s="295"/>
-      <c r="Z19" s="295"/>
-      <c r="AA19" s="295"/>
-      <c r="AB19" s="295"/>
-      <c r="AC19" s="295"/>
-      <c r="AD19" s="295"/>
-      <c r="AE19" s="295"/>
-      <c r="AF19" s="295"/>
-      <c r="AG19" s="295"/>
-      <c r="AH19" s="295"/>
-      <c r="AI19" s="295"/>
-      <c r="AJ19" s="295"/>
+      <c r="Q19" s="300"/>
+      <c r="R19" s="300"/>
+      <c r="S19" s="300"/>
+      <c r="T19" s="300"/>
+      <c r="U19" s="300"/>
+      <c r="V19" s="300"/>
+      <c r="W19" s="300"/>
+      <c r="X19" s="300"/>
+      <c r="Y19" s="300"/>
+      <c r="Z19" s="300"/>
+      <c r="AA19" s="300"/>
+      <c r="AB19" s="300"/>
+      <c r="AC19" s="300"/>
+      <c r="AD19" s="300"/>
+      <c r="AE19" s="300"/>
+      <c r="AF19" s="300"/>
+      <c r="AG19" s="300"/>
+      <c r="AH19" s="300"/>
+      <c r="AI19" s="300"/>
+      <c r="AJ19" s="300"/>
       <c r="AY19" s="186"/>
     </row>
     <row r="20" spans="1:51" ht="14.45" customHeight="1">
       <c r="A20" s="185"/>
-      <c r="Q20" s="295"/>
-      <c r="R20" s="295"/>
-      <c r="S20" s="295"/>
-      <c r="T20" s="295"/>
-      <c r="U20" s="295"/>
-      <c r="V20" s="295"/>
-      <c r="W20" s="295"/>
-      <c r="X20" s="295"/>
-      <c r="Y20" s="295"/>
-      <c r="Z20" s="295"/>
-      <c r="AA20" s="295"/>
-      <c r="AB20" s="295"/>
-      <c r="AC20" s="295"/>
-      <c r="AD20" s="295"/>
-      <c r="AE20" s="295"/>
-      <c r="AF20" s="295"/>
-      <c r="AG20" s="295"/>
-      <c r="AH20" s="295"/>
-      <c r="AI20" s="295"/>
-      <c r="AJ20" s="295"/>
+      <c r="Q20" s="300"/>
+      <c r="R20" s="300"/>
+      <c r="S20" s="300"/>
+      <c r="T20" s="300"/>
+      <c r="U20" s="300"/>
+      <c r="V20" s="300"/>
+      <c r="W20" s="300"/>
+      <c r="X20" s="300"/>
+      <c r="Y20" s="300"/>
+      <c r="Z20" s="300"/>
+      <c r="AA20" s="300"/>
+      <c r="AB20" s="300"/>
+      <c r="AC20" s="300"/>
+      <c r="AD20" s="300"/>
+      <c r="AE20" s="300"/>
+      <c r="AF20" s="300"/>
+      <c r="AG20" s="300"/>
+      <c r="AH20" s="300"/>
+      <c r="AI20" s="300"/>
+      <c r="AJ20" s="300"/>
       <c r="AY20" s="186"/>
     </row>
     <row r="21" spans="1:51" ht="14.45" customHeight="1">
       <c r="A21" s="185"/>
-      <c r="Q21" s="295"/>
-      <c r="R21" s="295"/>
-      <c r="S21" s="295"/>
-      <c r="T21" s="295"/>
-      <c r="U21" s="295"/>
-      <c r="V21" s="295"/>
-      <c r="W21" s="295"/>
-      <c r="X21" s="295"/>
-      <c r="Y21" s="295"/>
-      <c r="Z21" s="295"/>
-      <c r="AA21" s="295"/>
-      <c r="AB21" s="295"/>
-      <c r="AC21" s="295"/>
-      <c r="AD21" s="295"/>
-      <c r="AE21" s="295"/>
-      <c r="AF21" s="295"/>
-      <c r="AG21" s="295"/>
-      <c r="AH21" s="295"/>
-      <c r="AI21" s="295"/>
-      <c r="AJ21" s="295"/>
+      <c r="Q21" s="300"/>
+      <c r="R21" s="300"/>
+      <c r="S21" s="300"/>
+      <c r="T21" s="300"/>
+      <c r="U21" s="300"/>
+      <c r="V21" s="300"/>
+      <c r="W21" s="300"/>
+      <c r="X21" s="300"/>
+      <c r="Y21" s="300"/>
+      <c r="Z21" s="300"/>
+      <c r="AA21" s="300"/>
+      <c r="AB21" s="300"/>
+      <c r="AC21" s="300"/>
+      <c r="AD21" s="300"/>
+      <c r="AE21" s="300"/>
+      <c r="AF21" s="300"/>
+      <c r="AG21" s="300"/>
+      <c r="AH21" s="300"/>
+      <c r="AI21" s="300"/>
+      <c r="AJ21" s="300"/>
       <c r="AY21" s="186"/>
     </row>
     <row r="22" spans="1:51" ht="14.45" customHeight="1">
       <c r="A22" s="185"/>
-      <c r="Q22" s="295"/>
-      <c r="R22" s="295"/>
-      <c r="S22" s="295"/>
-      <c r="T22" s="295"/>
-      <c r="U22" s="295"/>
-      <c r="V22" s="295"/>
-      <c r="W22" s="295"/>
-      <c r="X22" s="295"/>
-      <c r="Y22" s="295"/>
-      <c r="Z22" s="295"/>
-      <c r="AA22" s="295"/>
-      <c r="AB22" s="295"/>
-      <c r="AC22" s="295"/>
-      <c r="AD22" s="295"/>
-      <c r="AE22" s="295"/>
-      <c r="AF22" s="295"/>
-      <c r="AG22" s="295"/>
-      <c r="AH22" s="295"/>
-      <c r="AI22" s="295"/>
-      <c r="AJ22" s="295"/>
+      <c r="Q22" s="300"/>
+      <c r="R22" s="300"/>
+      <c r="S22" s="300"/>
+      <c r="T22" s="300"/>
+      <c r="U22" s="300"/>
+      <c r="V22" s="300"/>
+      <c r="W22" s="300"/>
+      <c r="X22" s="300"/>
+      <c r="Y22" s="300"/>
+      <c r="Z22" s="300"/>
+      <c r="AA22" s="300"/>
+      <c r="AB22" s="300"/>
+      <c r="AC22" s="300"/>
+      <c r="AD22" s="300"/>
+      <c r="AE22" s="300"/>
+      <c r="AF22" s="300"/>
+      <c r="AG22" s="300"/>
+      <c r="AH22" s="300"/>
+      <c r="AI22" s="300"/>
+      <c r="AJ22" s="300"/>
       <c r="AY22" s="186"/>
     </row>
     <row r="23" spans="1:51" ht="14.45" customHeight="1">
@@ -24855,226 +24588,226 @@
       <c r="AY24" s="186"/>
     </row>
     <row r="25" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A25" s="296">
+      <c r="A25" s="301">
         <v>46112</v>
       </c>
-      <c r="B25" s="297"/>
-      <c r="C25" s="297"/>
-      <c r="D25" s="297"/>
-      <c r="E25" s="297"/>
-      <c r="F25" s="297"/>
-      <c r="G25" s="297"/>
-      <c r="H25" s="297"/>
-      <c r="I25" s="297"/>
-      <c r="J25" s="297"/>
-      <c r="K25" s="297"/>
-      <c r="L25" s="297"/>
-      <c r="M25" s="297"/>
-      <c r="N25" s="297"/>
-      <c r="O25" s="297"/>
-      <c r="P25" s="297"/>
-      <c r="Q25" s="297"/>
-      <c r="R25" s="297"/>
-      <c r="S25" s="297"/>
-      <c r="T25" s="297"/>
-      <c r="U25" s="297"/>
-      <c r="V25" s="297"/>
-      <c r="W25" s="297"/>
-      <c r="X25" s="297"/>
-      <c r="Y25" s="297"/>
-      <c r="Z25" s="297"/>
-      <c r="AA25" s="297"/>
-      <c r="AB25" s="297"/>
+      <c r="B25" s="302"/>
+      <c r="C25" s="302"/>
+      <c r="D25" s="302"/>
+      <c r="E25" s="302"/>
+      <c r="F25" s="302"/>
+      <c r="G25" s="302"/>
+      <c r="H25" s="302"/>
+      <c r="I25" s="302"/>
+      <c r="J25" s="302"/>
+      <c r="K25" s="302"/>
+      <c r="L25" s="302"/>
+      <c r="M25" s="302"/>
+      <c r="N25" s="302"/>
+      <c r="O25" s="302"/>
+      <c r="P25" s="302"/>
+      <c r="Q25" s="302"/>
+      <c r="R25" s="302"/>
+      <c r="S25" s="302"/>
+      <c r="T25" s="302"/>
+      <c r="U25" s="302"/>
+      <c r="V25" s="302"/>
+      <c r="W25" s="302"/>
+      <c r="X25" s="302"/>
+      <c r="Y25" s="302"/>
+      <c r="Z25" s="302"/>
+      <c r="AA25" s="302"/>
+      <c r="AB25" s="302"/>
       <c r="AC25" s="188"/>
-      <c r="AD25" s="298">
+      <c r="AD25" s="303">
         <v>1</v>
       </c>
-      <c r="AE25" s="298"/>
-      <c r="AF25" s="298"/>
-      <c r="AG25" s="298"/>
-      <c r="AH25" s="298"/>
-      <c r="AI25" s="298"/>
-      <c r="AJ25" s="298"/>
-      <c r="AK25" s="298"/>
-      <c r="AL25" s="298"/>
-      <c r="AM25" s="298"/>
-      <c r="AN25" s="298"/>
-      <c r="AO25" s="298"/>
-      <c r="AP25" s="298"/>
-      <c r="AQ25" s="298"/>
-      <c r="AR25" s="298"/>
-      <c r="AS25" s="298"/>
-      <c r="AT25" s="298"/>
-      <c r="AU25" s="298"/>
-      <c r="AV25" s="298"/>
-      <c r="AW25" s="298"/>
-      <c r="AX25" s="298"/>
-      <c r="AY25" s="299"/>
+      <c r="AE25" s="303"/>
+      <c r="AF25" s="303"/>
+      <c r="AG25" s="303"/>
+      <c r="AH25" s="303"/>
+      <c r="AI25" s="303"/>
+      <c r="AJ25" s="303"/>
+      <c r="AK25" s="303"/>
+      <c r="AL25" s="303"/>
+      <c r="AM25" s="303"/>
+      <c r="AN25" s="303"/>
+      <c r="AO25" s="303"/>
+      <c r="AP25" s="303"/>
+      <c r="AQ25" s="303"/>
+      <c r="AR25" s="303"/>
+      <c r="AS25" s="303"/>
+      <c r="AT25" s="303"/>
+      <c r="AU25" s="303"/>
+      <c r="AV25" s="303"/>
+      <c r="AW25" s="303"/>
+      <c r="AX25" s="303"/>
+      <c r="AY25" s="304"/>
     </row>
     <row r="26" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A26" s="296"/>
-      <c r="B26" s="297"/>
-      <c r="C26" s="297"/>
-      <c r="D26" s="297"/>
-      <c r="E26" s="297"/>
-      <c r="F26" s="297"/>
-      <c r="G26" s="297"/>
-      <c r="H26" s="297"/>
-      <c r="I26" s="297"/>
-      <c r="J26" s="297"/>
-      <c r="K26" s="297"/>
-      <c r="L26" s="297"/>
-      <c r="M26" s="297"/>
-      <c r="N26" s="297"/>
-      <c r="O26" s="297"/>
-      <c r="P26" s="297"/>
-      <c r="Q26" s="297"/>
-      <c r="R26" s="297"/>
-      <c r="S26" s="297"/>
-      <c r="T26" s="297"/>
-      <c r="U26" s="297"/>
-      <c r="V26" s="297"/>
-      <c r="W26" s="297"/>
-      <c r="X26" s="297"/>
-      <c r="Y26" s="297"/>
-      <c r="Z26" s="297"/>
-      <c r="AA26" s="297"/>
-      <c r="AB26" s="297"/>
+      <c r="A26" s="301"/>
+      <c r="B26" s="302"/>
+      <c r="C26" s="302"/>
+      <c r="D26" s="302"/>
+      <c r="E26" s="302"/>
+      <c r="F26" s="302"/>
+      <c r="G26" s="302"/>
+      <c r="H26" s="302"/>
+      <c r="I26" s="302"/>
+      <c r="J26" s="302"/>
+      <c r="K26" s="302"/>
+      <c r="L26" s="302"/>
+      <c r="M26" s="302"/>
+      <c r="N26" s="302"/>
+      <c r="O26" s="302"/>
+      <c r="P26" s="302"/>
+      <c r="Q26" s="302"/>
+      <c r="R26" s="302"/>
+      <c r="S26" s="302"/>
+      <c r="T26" s="302"/>
+      <c r="U26" s="302"/>
+      <c r="V26" s="302"/>
+      <c r="W26" s="302"/>
+      <c r="X26" s="302"/>
+      <c r="Y26" s="302"/>
+      <c r="Z26" s="302"/>
+      <c r="AA26" s="302"/>
+      <c r="AB26" s="302"/>
       <c r="AC26" s="188"/>
-      <c r="AD26" s="298"/>
-      <c r="AE26" s="298"/>
-      <c r="AF26" s="298"/>
-      <c r="AG26" s="298"/>
-      <c r="AH26" s="298"/>
-      <c r="AI26" s="298"/>
-      <c r="AJ26" s="298"/>
-      <c r="AK26" s="298"/>
-      <c r="AL26" s="298"/>
-      <c r="AM26" s="298"/>
-      <c r="AN26" s="298"/>
-      <c r="AO26" s="298"/>
-      <c r="AP26" s="298"/>
-      <c r="AQ26" s="298"/>
-      <c r="AR26" s="298"/>
-      <c r="AS26" s="298"/>
-      <c r="AT26" s="298"/>
-      <c r="AU26" s="298"/>
-      <c r="AV26" s="298"/>
-      <c r="AW26" s="298"/>
-      <c r="AX26" s="298"/>
-      <c r="AY26" s="299"/>
+      <c r="AD26" s="303"/>
+      <c r="AE26" s="303"/>
+      <c r="AF26" s="303"/>
+      <c r="AG26" s="303"/>
+      <c r="AH26" s="303"/>
+      <c r="AI26" s="303"/>
+      <c r="AJ26" s="303"/>
+      <c r="AK26" s="303"/>
+      <c r="AL26" s="303"/>
+      <c r="AM26" s="303"/>
+      <c r="AN26" s="303"/>
+      <c r="AO26" s="303"/>
+      <c r="AP26" s="303"/>
+      <c r="AQ26" s="303"/>
+      <c r="AR26" s="303"/>
+      <c r="AS26" s="303"/>
+      <c r="AT26" s="303"/>
+      <c r="AU26" s="303"/>
+      <c r="AV26" s="303"/>
+      <c r="AW26" s="303"/>
+      <c r="AX26" s="303"/>
+      <c r="AY26" s="304"/>
     </row>
     <row r="27" spans="1:51" ht="14.45" customHeight="1">
       <c r="A27" s="185"/>
       <c r="AY27" s="186"/>
     </row>
     <row r="28" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A28" s="292" t="s">
+      <c r="A28" s="297" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="293"/>
-      <c r="C28" s="293"/>
-      <c r="D28" s="293"/>
-      <c r="E28" s="293"/>
-      <c r="F28" s="293"/>
-      <c r="G28" s="293"/>
-      <c r="H28" s="293"/>
-      <c r="I28" s="293"/>
-      <c r="J28" s="293"/>
-      <c r="K28" s="293"/>
-      <c r="L28" s="293"/>
-      <c r="M28" s="293"/>
-      <c r="N28" s="293"/>
-      <c r="O28" s="293"/>
-      <c r="P28" s="293"/>
-      <c r="Q28" s="293"/>
-      <c r="R28" s="293"/>
-      <c r="S28" s="293"/>
-      <c r="T28" s="293"/>
-      <c r="U28" s="293"/>
-      <c r="V28" s="293"/>
-      <c r="W28" s="293"/>
-      <c r="X28" s="293"/>
-      <c r="Y28" s="293"/>
-      <c r="Z28" s="293"/>
-      <c r="AA28" s="293"/>
-      <c r="AB28" s="293"/>
-      <c r="AC28" s="293"/>
-      <c r="AD28" s="293"/>
-      <c r="AE28" s="293"/>
-      <c r="AF28" s="293"/>
-      <c r="AG28" s="293"/>
-      <c r="AH28" s="293"/>
-      <c r="AI28" s="293"/>
-      <c r="AJ28" s="293"/>
-      <c r="AK28" s="293"/>
-      <c r="AL28" s="293"/>
-      <c r="AM28" s="293"/>
-      <c r="AN28" s="293"/>
-      <c r="AO28" s="293"/>
-      <c r="AP28" s="293"/>
-      <c r="AQ28" s="293"/>
-      <c r="AR28" s="293"/>
-      <c r="AS28" s="293"/>
-      <c r="AT28" s="293"/>
-      <c r="AU28" s="293"/>
-      <c r="AV28" s="293"/>
-      <c r="AW28" s="293"/>
-      <c r="AX28" s="293"/>
-      <c r="AY28" s="294"/>
+      <c r="B28" s="298"/>
+      <c r="C28" s="298"/>
+      <c r="D28" s="298"/>
+      <c r="E28" s="298"/>
+      <c r="F28" s="298"/>
+      <c r="G28" s="298"/>
+      <c r="H28" s="298"/>
+      <c r="I28" s="298"/>
+      <c r="J28" s="298"/>
+      <c r="K28" s="298"/>
+      <c r="L28" s="298"/>
+      <c r="M28" s="298"/>
+      <c r="N28" s="298"/>
+      <c r="O28" s="298"/>
+      <c r="P28" s="298"/>
+      <c r="Q28" s="298"/>
+      <c r="R28" s="298"/>
+      <c r="S28" s="298"/>
+      <c r="T28" s="298"/>
+      <c r="U28" s="298"/>
+      <c r="V28" s="298"/>
+      <c r="W28" s="298"/>
+      <c r="X28" s="298"/>
+      <c r="Y28" s="298"/>
+      <c r="Z28" s="298"/>
+      <c r="AA28" s="298"/>
+      <c r="AB28" s="298"/>
+      <c r="AC28" s="298"/>
+      <c r="AD28" s="298"/>
+      <c r="AE28" s="298"/>
+      <c r="AF28" s="298"/>
+      <c r="AG28" s="298"/>
+      <c r="AH28" s="298"/>
+      <c r="AI28" s="298"/>
+      <c r="AJ28" s="298"/>
+      <c r="AK28" s="298"/>
+      <c r="AL28" s="298"/>
+      <c r="AM28" s="298"/>
+      <c r="AN28" s="298"/>
+      <c r="AO28" s="298"/>
+      <c r="AP28" s="298"/>
+      <c r="AQ28" s="298"/>
+      <c r="AR28" s="298"/>
+      <c r="AS28" s="298"/>
+      <c r="AT28" s="298"/>
+      <c r="AU28" s="298"/>
+      <c r="AV28" s="298"/>
+      <c r="AW28" s="298"/>
+      <c r="AX28" s="298"/>
+      <c r="AY28" s="299"/>
     </row>
     <row r="29" spans="1:51" ht="14.45" customHeight="1">
-      <c r="A29" s="292"/>
-      <c r="B29" s="293"/>
-      <c r="C29" s="293"/>
-      <c r="D29" s="293"/>
-      <c r="E29" s="293"/>
-      <c r="F29" s="293"/>
-      <c r="G29" s="293"/>
-      <c r="H29" s="293"/>
-      <c r="I29" s="293"/>
-      <c r="J29" s="293"/>
-      <c r="K29" s="293"/>
-      <c r="L29" s="293"/>
-      <c r="M29" s="293"/>
-      <c r="N29" s="293"/>
-      <c r="O29" s="293"/>
-      <c r="P29" s="293"/>
-      <c r="Q29" s="293"/>
-      <c r="R29" s="293"/>
-      <c r="S29" s="293"/>
-      <c r="T29" s="293"/>
-      <c r="U29" s="293"/>
-      <c r="V29" s="293"/>
-      <c r="W29" s="293"/>
-      <c r="X29" s="293"/>
-      <c r="Y29" s="293"/>
-      <c r="Z29" s="293"/>
-      <c r="AA29" s="293"/>
-      <c r="AB29" s="293"/>
-      <c r="AC29" s="293"/>
-      <c r="AD29" s="293"/>
-      <c r="AE29" s="293"/>
-      <c r="AF29" s="293"/>
-      <c r="AG29" s="293"/>
-      <c r="AH29" s="293"/>
-      <c r="AI29" s="293"/>
-      <c r="AJ29" s="293"/>
-      <c r="AK29" s="293"/>
-      <c r="AL29" s="293"/>
-      <c r="AM29" s="293"/>
-      <c r="AN29" s="293"/>
-      <c r="AO29" s="293"/>
-      <c r="AP29" s="293"/>
-      <c r="AQ29" s="293"/>
-      <c r="AR29" s="293"/>
-      <c r="AS29" s="293"/>
-      <c r="AT29" s="293"/>
-      <c r="AU29" s="293"/>
-      <c r="AV29" s="293"/>
-      <c r="AW29" s="293"/>
-      <c r="AX29" s="293"/>
-      <c r="AY29" s="294"/>
+      <c r="A29" s="297"/>
+      <c r="B29" s="298"/>
+      <c r="C29" s="298"/>
+      <c r="D29" s="298"/>
+      <c r="E29" s="298"/>
+      <c r="F29" s="298"/>
+      <c r="G29" s="298"/>
+      <c r="H29" s="298"/>
+      <c r="I29" s="298"/>
+      <c r="J29" s="298"/>
+      <c r="K29" s="298"/>
+      <c r="L29" s="298"/>
+      <c r="M29" s="298"/>
+      <c r="N29" s="298"/>
+      <c r="O29" s="298"/>
+      <c r="P29" s="298"/>
+      <c r="Q29" s="298"/>
+      <c r="R29" s="298"/>
+      <c r="S29" s="298"/>
+      <c r="T29" s="298"/>
+      <c r="U29" s="298"/>
+      <c r="V29" s="298"/>
+      <c r="W29" s="298"/>
+      <c r="X29" s="298"/>
+      <c r="Y29" s="298"/>
+      <c r="Z29" s="298"/>
+      <c r="AA29" s="298"/>
+      <c r="AB29" s="298"/>
+      <c r="AC29" s="298"/>
+      <c r="AD29" s="298"/>
+      <c r="AE29" s="298"/>
+      <c r="AF29" s="298"/>
+      <c r="AG29" s="298"/>
+      <c r="AH29" s="298"/>
+      <c r="AI29" s="298"/>
+      <c r="AJ29" s="298"/>
+      <c r="AK29" s="298"/>
+      <c r="AL29" s="298"/>
+      <c r="AM29" s="298"/>
+      <c r="AN29" s="298"/>
+      <c r="AO29" s="298"/>
+      <c r="AP29" s="298"/>
+      <c r="AQ29" s="298"/>
+      <c r="AR29" s="298"/>
+      <c r="AS29" s="298"/>
+      <c r="AT29" s="298"/>
+      <c r="AU29" s="298"/>
+      <c r="AV29" s="298"/>
+      <c r="AW29" s="298"/>
+      <c r="AX29" s="298"/>
+      <c r="AY29" s="299"/>
     </row>
     <row r="30" spans="1:51" ht="14.45" customHeight="1">
       <c r="A30" s="185"/>
@@ -25148,13 +24881,6 @@
     <protectedRange sqref="AZ1:XFD1048576" name="メモ欄1"/>
   </protectedRanges>
   <mergeCells count="15">
-    <mergeCell ref="A28:AY29"/>
-    <mergeCell ref="Q19:U22"/>
-    <mergeCell ref="V19:Z22"/>
-    <mergeCell ref="AA19:AE22"/>
-    <mergeCell ref="AF19:AJ22"/>
-    <mergeCell ref="A25:AB26"/>
-    <mergeCell ref="AD25:AY26"/>
     <mergeCell ref="C3:AY4"/>
     <mergeCell ref="A6:AY10"/>
     <mergeCell ref="A11:AY13"/>
@@ -25163,6 +24889,13 @@
     <mergeCell ref="V18:Z18"/>
     <mergeCell ref="AA18:AE18"/>
     <mergeCell ref="AF18:AJ18"/>
+    <mergeCell ref="A28:AY29"/>
+    <mergeCell ref="Q19:U22"/>
+    <mergeCell ref="V19:Z22"/>
+    <mergeCell ref="AA19:AE22"/>
+    <mergeCell ref="AF19:AJ22"/>
+    <mergeCell ref="A25:AB26"/>
+    <mergeCell ref="AD25:AY26"/>
   </mergeCells>
   <phoneticPr fontId="16"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -25328,16 +25061,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="55" customFormat="1" ht="15">
-      <c r="A1" s="300" t="s">
+      <c r="A1" s="314" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="300"/>
-      <c r="C1" s="300"/>
-      <c r="D1" s="301" t="s">
+      <c r="B1" s="314"/>
+      <c r="C1" s="314"/>
+      <c r="D1" s="315" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="302"/>
-      <c r="F1" s="302"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
       <c r="G1" s="51" t="s">
         <v>4</v>
       </c>
@@ -25354,12 +25087,12 @@
       <c r="L1" s="54"/>
     </row>
     <row r="2" spans="1:13" s="55" customFormat="1" ht="15">
-      <c r="A2" s="300"/>
-      <c r="B2" s="300"/>
-      <c r="C2" s="300"/>
-      <c r="D2" s="302"/>
-      <c r="E2" s="302"/>
-      <c r="F2" s="302"/>
+      <c r="A2" s="314"/>
+      <c r="B2" s="314"/>
+      <c r="C2" s="314"/>
+      <c r="D2" s="316"/>
+      <c r="E2" s="316"/>
+      <c r="F2" s="316"/>
       <c r="G2" s="56">
         <f>COUNTA(C4:C1048576)</f>
         <v>22</v>
@@ -25380,11 +25113,11 @@
       <c r="L2" s="54"/>
     </row>
     <row r="3" spans="1:13" s="55" customFormat="1" ht="15">
-      <c r="A3" s="303" t="s">
+      <c r="A3" s="317" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="303"/>
-      <c r="C3" s="303"/>
+      <c r="B3" s="317"/>
+      <c r="C3" s="317"/>
       <c r="D3" s="58" t="s">
         <v>45</v>
       </c>
@@ -25409,7 +25142,7 @@
       <c r="K3" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="320" t="s">
+      <c r="L3" s="283" t="s">
         <v>44</v>
       </c>
       <c r="M3" s="58" t="s">
@@ -25432,7 +25165,7 @@
       <c r="I4" s="66"/>
       <c r="J4" s="68"/>
       <c r="K4" s="69"/>
-      <c r="L4" s="321"/>
+      <c r="L4" s="284"/>
       <c r="M4" s="70"/>
     </row>
     <row r="5" spans="1:13" ht="15">
@@ -25451,7 +25184,7 @@
       <c r="I5" s="79"/>
       <c r="J5" s="80"/>
       <c r="K5" s="81"/>
-      <c r="L5" s="322"/>
+      <c r="L5" s="285"/>
       <c r="M5" s="82"/>
     </row>
     <row r="6" spans="1:13" ht="15">
@@ -25474,8 +25207,8 @@
       <c r="I6" s="88"/>
       <c r="J6" s="89"/>
       <c r="K6" s="90"/>
-      <c r="L6" s="323" t="s">
-        <v>151</v>
+      <c r="L6" s="286" t="s">
+        <v>150</v>
       </c>
       <c r="M6" s="91"/>
     </row>
@@ -25495,7 +25228,7 @@
       <c r="I7" s="94"/>
       <c r="J7" s="76"/>
       <c r="K7" s="81"/>
-      <c r="L7" s="324"/>
+      <c r="L7" s="287"/>
       <c r="M7" s="95"/>
     </row>
     <row r="8" spans="1:13" ht="15">
@@ -25518,8 +25251,8 @@
       <c r="I8" s="99"/>
       <c r="J8" s="96"/>
       <c r="K8" s="89"/>
-      <c r="L8" s="323" t="s">
-        <v>151</v>
+      <c r="L8" s="286" t="s">
+        <v>150</v>
       </c>
       <c r="M8" s="100"/>
     </row>
@@ -25542,7 +25275,7 @@
       <c r="J9" s="103"/>
       <c r="K9" s="107"/>
       <c r="L9" s="218" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M9" s="108"/>
     </row>
@@ -25562,7 +25295,7 @@
       <c r="I10" s="66"/>
       <c r="J10" s="68"/>
       <c r="K10" s="69"/>
-      <c r="L10" s="325"/>
+      <c r="L10" s="288"/>
       <c r="M10" s="70"/>
     </row>
     <row r="11" spans="1:13" ht="15">
@@ -25581,7 +25314,7 @@
       <c r="I11" s="79"/>
       <c r="J11" s="80"/>
       <c r="K11" s="81"/>
-      <c r="L11" s="324"/>
+      <c r="L11" s="287"/>
       <c r="M11" s="111"/>
     </row>
     <row r="12" spans="1:13" ht="15">
@@ -25602,8 +25335,8 @@
       <c r="I12" s="115"/>
       <c r="J12" s="116"/>
       <c r="K12" s="116"/>
-      <c r="L12" s="326" t="s">
-        <v>151</v>
+      <c r="L12" s="289" t="s">
+        <v>150</v>
       </c>
       <c r="M12" s="117"/>
     </row>
@@ -25623,7 +25356,7 @@
       <c r="I13" s="79"/>
       <c r="J13" s="80"/>
       <c r="K13" s="81"/>
-      <c r="L13" s="324"/>
+      <c r="L13" s="287"/>
       <c r="M13" s="111"/>
     </row>
     <row r="14" spans="1:13" ht="30">
@@ -25646,8 +25379,8 @@
       <c r="I14" s="88"/>
       <c r="J14" s="89"/>
       <c r="K14" s="89"/>
-      <c r="L14" s="323" t="s">
-        <v>151</v>
+      <c r="L14" s="286" t="s">
+        <v>150</v>
       </c>
       <c r="M14" s="91"/>
     </row>
@@ -25670,7 +25403,7 @@
       <c r="J15" s="107"/>
       <c r="K15" s="107"/>
       <c r="L15" s="218" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M15" s="119"/>
     </row>
@@ -25690,7 +25423,7 @@
       <c r="I16" s="66"/>
       <c r="J16" s="68"/>
       <c r="K16" s="69"/>
-      <c r="L16" s="325"/>
+      <c r="L16" s="288"/>
       <c r="M16" s="70"/>
     </row>
     <row r="17" spans="1:13" ht="15">
@@ -25709,7 +25442,7 @@
       <c r="I17" s="79"/>
       <c r="J17" s="80"/>
       <c r="K17" s="81"/>
-      <c r="L17" s="324"/>
+      <c r="L17" s="287"/>
       <c r="M17" s="111"/>
     </row>
     <row r="18" spans="1:13" ht="15">
@@ -25730,8 +25463,8 @@
       <c r="I18" s="115"/>
       <c r="J18" s="116"/>
       <c r="K18" s="116"/>
-      <c r="L18" s="326" t="s">
-        <v>151</v>
+      <c r="L18" s="289" t="s">
+        <v>150</v>
       </c>
       <c r="M18" s="117"/>
     </row>
@@ -25751,7 +25484,7 @@
       <c r="I19" s="94"/>
       <c r="J19" s="76"/>
       <c r="K19" s="81"/>
-      <c r="L19" s="324"/>
+      <c r="L19" s="287"/>
       <c r="M19" s="95"/>
     </row>
     <row r="20" spans="1:13" ht="105">
@@ -25772,8 +25505,8 @@
       <c r="I20" s="99"/>
       <c r="J20" s="96"/>
       <c r="K20" s="89"/>
-      <c r="L20" s="323" t="s">
-        <v>151</v>
+      <c r="L20" s="286" t="s">
+        <v>150</v>
       </c>
       <c r="M20" s="214" t="s">
         <v>131</v>
@@ -25797,8 +25530,8 @@
       <c r="I21" s="124"/>
       <c r="J21" s="125"/>
       <c r="K21" s="126"/>
-      <c r="L21" s="327" t="s">
-        <v>151</v>
+      <c r="L21" s="290" t="s">
+        <v>150</v>
       </c>
       <c r="M21" s="214" t="s">
         <v>132</v>
@@ -25822,8 +25555,8 @@
       <c r="I22" s="174"/>
       <c r="J22" s="175"/>
       <c r="K22" s="146"/>
-      <c r="L22" s="328" t="s">
-        <v>152</v>
+      <c r="L22" s="291" t="s">
+        <v>151</v>
       </c>
       <c r="M22" s="215" t="s">
         <v>130</v>
@@ -25845,7 +25578,7 @@
       <c r="I23" s="129"/>
       <c r="J23" s="65"/>
       <c r="K23" s="69"/>
-      <c r="L23" s="325"/>
+      <c r="L23" s="288"/>
       <c r="M23" s="130"/>
     </row>
     <row r="24" spans="1:13" s="2" customFormat="1" ht="15">
@@ -25864,7 +25597,7 @@
       <c r="I24" s="136"/>
       <c r="J24" s="133"/>
       <c r="K24" s="137"/>
-      <c r="L24" s="329"/>
+      <c r="L24" s="292"/>
       <c r="M24" s="139"/>
     </row>
     <row r="25" spans="1:13" s="2" customFormat="1" ht="15">
@@ -25887,8 +25620,8 @@
       <c r="I25" s="142"/>
       <c r="J25" s="46"/>
       <c r="K25" s="143"/>
-      <c r="L25" s="323" t="s">
-        <v>151</v>
+      <c r="L25" s="286" t="s">
+        <v>150</v>
       </c>
       <c r="M25" s="100"/>
     </row>
@@ -25910,8 +25643,8 @@
       <c r="I26" s="145"/>
       <c r="J26" s="33"/>
       <c r="K26" s="146"/>
-      <c r="L26" s="330" t="s">
-        <v>151</v>
+      <c r="L26" s="293" t="s">
+        <v>150</v>
       </c>
       <c r="M26" s="108"/>
     </row>
@@ -25931,7 +25664,7 @@
       <c r="I27" s="136"/>
       <c r="J27" s="133"/>
       <c r="K27" s="137"/>
-      <c r="L27" s="329"/>
+      <c r="L27" s="292"/>
       <c r="M27" s="139"/>
     </row>
     <row r="28" spans="1:13" s="2" customFormat="1" ht="75">
@@ -25954,8 +25687,8 @@
       <c r="I28" s="142"/>
       <c r="J28" s="46"/>
       <c r="K28" s="143"/>
-      <c r="L28" s="323" t="s">
-        <v>151</v>
+      <c r="L28" s="286" t="s">
+        <v>150</v>
       </c>
       <c r="M28" s="100"/>
     </row>
@@ -25977,8 +25710,8 @@
       <c r="I29" s="148"/>
       <c r="J29" s="37"/>
       <c r="K29" s="149"/>
-      <c r="L29" s="327" t="s">
-        <v>151</v>
+      <c r="L29" s="290" t="s">
+        <v>150</v>
       </c>
       <c r="M29" s="127"/>
     </row>
@@ -26000,8 +25733,8 @@
       <c r="I30" s="145"/>
       <c r="J30" s="33"/>
       <c r="K30" s="146"/>
-      <c r="L30" s="330" t="s">
-        <v>151</v>
+      <c r="L30" s="293" t="s">
+        <v>150</v>
       </c>
       <c r="M30" s="108"/>
     </row>
@@ -26021,7 +25754,7 @@
       <c r="I31" s="129"/>
       <c r="J31" s="65"/>
       <c r="K31" s="69"/>
-      <c r="L31" s="325"/>
+      <c r="L31" s="288"/>
       <c r="M31" s="130"/>
     </row>
     <row r="32" spans="1:13" s="2" customFormat="1" ht="15">
@@ -26040,7 +25773,7 @@
       <c r="I32" s="136"/>
       <c r="J32" s="133"/>
       <c r="K32" s="137"/>
-      <c r="L32" s="329"/>
+      <c r="L32" s="292"/>
       <c r="M32" s="139"/>
     </row>
     <row r="33" spans="1:13" s="2" customFormat="1" ht="30">
@@ -26061,8 +25794,8 @@
       <c r="I33" s="142"/>
       <c r="J33" s="46"/>
       <c r="K33" s="143"/>
-      <c r="L33" s="323" t="s">
-        <v>151</v>
+      <c r="L33" s="286" t="s">
+        <v>150</v>
       </c>
       <c r="M33" s="100"/>
     </row>
@@ -26082,7 +25815,7 @@
       <c r="I34" s="151"/>
       <c r="J34" s="153"/>
       <c r="K34" s="154"/>
-      <c r="L34" s="331"/>
+      <c r="L34" s="294"/>
       <c r="M34" s="155"/>
     </row>
     <row r="35" spans="1:13" s="2" customFormat="1" ht="120">
@@ -26105,8 +25838,8 @@
       <c r="I35" s="261"/>
       <c r="J35" s="263"/>
       <c r="K35" s="264"/>
-      <c r="L35" s="332" t="s">
-        <v>151</v>
+      <c r="L35" s="295" t="s">
+        <v>150</v>
       </c>
       <c r="M35" s="265"/>
     </row>
@@ -26126,7 +25859,7 @@
       <c r="I36" s="136"/>
       <c r="J36" s="133"/>
       <c r="K36" s="137"/>
-      <c r="L36" s="329"/>
+      <c r="L36" s="292"/>
       <c r="M36" s="139"/>
     </row>
     <row r="37" spans="1:13" s="2" customFormat="1" ht="75">
@@ -26147,8 +25880,8 @@
       <c r="I37" s="142"/>
       <c r="J37" s="46"/>
       <c r="K37" s="143"/>
-      <c r="L37" s="323" t="s">
-        <v>151</v>
+      <c r="L37" s="286" t="s">
+        <v>150</v>
       </c>
       <c r="M37" s="100"/>
     </row>
@@ -26168,7 +25901,7 @@
       <c r="I38" s="94"/>
       <c r="J38" s="76"/>
       <c r="K38" s="81"/>
-      <c r="L38" s="324"/>
+      <c r="L38" s="287"/>
       <c r="M38" s="95"/>
     </row>
     <row r="39" spans="1:13" ht="45">
@@ -26189,8 +25922,8 @@
       <c r="I39" s="161"/>
       <c r="J39" s="114"/>
       <c r="K39" s="162"/>
-      <c r="L39" s="326" t="s">
-        <v>151</v>
+      <c r="L39" s="289" t="s">
+        <v>150</v>
       </c>
       <c r="M39" s="163"/>
     </row>
@@ -26210,7 +25943,7 @@
       <c r="I40" s="129"/>
       <c r="J40" s="65"/>
       <c r="K40" s="69"/>
-      <c r="L40" s="325"/>
+      <c r="L40" s="288"/>
       <c r="M40" s="130"/>
     </row>
     <row r="41" spans="1:13" s="2" customFormat="1" ht="15">
@@ -26229,7 +25962,7 @@
       <c r="I41" s="136"/>
       <c r="J41" s="133"/>
       <c r="K41" s="137"/>
-      <c r="L41" s="329"/>
+      <c r="L41" s="292"/>
       <c r="M41" s="139"/>
     </row>
     <row r="42" spans="1:13" s="2" customFormat="1" ht="15">
@@ -26250,8 +25983,8 @@
       <c r="I42" s="142"/>
       <c r="J42" s="46"/>
       <c r="K42" s="143"/>
-      <c r="L42" s="323" t="s">
-        <v>151</v>
+      <c r="L42" s="286" t="s">
+        <v>150</v>
       </c>
       <c r="M42" s="100"/>
     </row>
@@ -26271,7 +26004,7 @@
       <c r="I43" s="129"/>
       <c r="J43" s="65"/>
       <c r="K43" s="69"/>
-      <c r="L43" s="325"/>
+      <c r="L43" s="288"/>
       <c r="M43" s="130"/>
     </row>
     <row r="44" spans="1:13" ht="15">
@@ -26290,7 +26023,7 @@
       <c r="I44" s="94"/>
       <c r="J44" s="76"/>
       <c r="K44" s="81"/>
-      <c r="L44" s="324"/>
+      <c r="L44" s="287"/>
       <c r="M44" s="95"/>
     </row>
     <row r="45" spans="1:13" ht="30">
@@ -26313,8 +26046,8 @@
       <c r="I45" s="99"/>
       <c r="J45" s="96"/>
       <c r="K45" s="90"/>
-      <c r="L45" s="323" t="s">
-        <v>151</v>
+      <c r="L45" s="286" t="s">
+        <v>150</v>
       </c>
       <c r="M45" s="100"/>
     </row>
@@ -26336,8 +26069,8 @@
       <c r="I46" s="106"/>
       <c r="J46" s="103"/>
       <c r="K46" s="146"/>
-      <c r="L46" s="330" t="s">
-        <v>151</v>
+      <c r="L46" s="293" t="s">
+        <v>150</v>
       </c>
       <c r="M46" s="108"/>
     </row>
@@ -26376,16 +26109,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="304" t="s">
+      <c r="A1" s="318" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-      <c r="D1" s="306" t="s">
+      <c r="B1" s="318"/>
+      <c r="C1" s="318"/>
+      <c r="D1" s="320" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="306"/>
-      <c r="F1" s="306"/>
+      <c r="E1" s="320"/>
+      <c r="F1" s="320"/>
       <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
@@ -26402,12 +26135,12 @@
       <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="304"/>
-      <c r="B2" s="304"/>
-      <c r="C2" s="304"/>
-      <c r="D2" s="307"/>
-      <c r="E2" s="307"/>
-      <c r="F2" s="307"/>
+      <c r="A2" s="318"/>
+      <c r="B2" s="318"/>
+      <c r="C2" s="318"/>
+      <c r="D2" s="321"/>
+      <c r="E2" s="321"/>
+      <c r="F2" s="321"/>
       <c r="G2" s="5">
         <f>COUNTA(C4:C1048576)</f>
         <v>12</v>
@@ -26428,11 +26161,11 @@
       <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="305" t="s">
+      <c r="A3" s="319" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="305"/>
-      <c r="C3" s="305"/>
+      <c r="B3" s="319"/>
+      <c r="C3" s="319"/>
       <c r="D3" s="18" t="s">
         <v>45</v>
       </c>
@@ -26522,8 +26255,8 @@
       <c r="I6" s="142"/>
       <c r="J6" s="237"/>
       <c r="K6" s="238"/>
-      <c r="L6" s="333" t="s">
-        <v>151</v>
+      <c r="L6" s="296" t="s">
+        <v>150</v>
       </c>
       <c r="M6" s="40"/>
     </row>
@@ -26566,8 +26299,8 @@
       <c r="I8" s="142"/>
       <c r="J8" s="237"/>
       <c r="K8" s="238"/>
-      <c r="L8" s="333" t="s">
-        <v>151</v>
+      <c r="L8" s="296" t="s">
+        <v>150</v>
       </c>
       <c r="M8" s="180"/>
     </row>
@@ -26629,8 +26362,8 @@
       <c r="I11" s="142"/>
       <c r="J11" s="237"/>
       <c r="K11" s="238"/>
-      <c r="L11" s="333" t="s">
-        <v>151</v>
+      <c r="L11" s="296" t="s">
+        <v>150</v>
       </c>
       <c r="M11" s="40"/>
     </row>
@@ -26653,7 +26386,7 @@
       <c r="J12" s="249"/>
       <c r="K12" s="156"/>
       <c r="L12" s="168" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M12" s="42"/>
     </row>
@@ -26676,7 +26409,7 @@
       <c r="J13" s="249"/>
       <c r="K13" s="156"/>
       <c r="L13" s="168" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M13" s="42"/>
     </row>
@@ -26699,7 +26432,7 @@
       <c r="J14" s="249"/>
       <c r="K14" s="156"/>
       <c r="L14" s="168" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M14" s="42"/>
     </row>
@@ -26722,7 +26455,7 @@
       <c r="J15" s="250"/>
       <c r="K15" s="170"/>
       <c r="L15" s="169" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M15" s="41"/>
     </row>
@@ -26765,8 +26498,8 @@
       <c r="I17" s="142"/>
       <c r="J17" s="256"/>
       <c r="K17" s="238"/>
-      <c r="L17" s="333" t="s">
-        <v>151</v>
+      <c r="L17" s="296" t="s">
+        <v>150</v>
       </c>
       <c r="M17" s="40"/>
     </row>
@@ -26789,7 +26522,7 @@
       <c r="J18" s="257"/>
       <c r="K18" s="156"/>
       <c r="L18" s="168" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M18" s="42"/>
     </row>
@@ -26812,7 +26545,7 @@
       <c r="J19" s="249"/>
       <c r="K19" s="156"/>
       <c r="L19" s="168" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M19" s="42"/>
     </row>
@@ -26835,7 +26568,7 @@
       <c r="J20" s="249"/>
       <c r="K20" s="156"/>
       <c r="L20" s="168" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M20" s="42"/>
     </row>
@@ -26858,7 +26591,7 @@
       <c r="J21" s="218"/>
       <c r="K21" s="170"/>
       <c r="L21" s="169" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M21" s="41"/>
     </row>
@@ -26877,7 +26610,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CY51"/>
@@ -26911,13 +26643,13 @@
       <c r="CY1" s="200"/>
     </row>
     <row r="2" spans="1:103">
-      <c r="B2" s="308" t="s">
+      <c r="B2" s="322" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="309"/>
-      <c r="D2" s="309"/>
-      <c r="E2" s="309"/>
-      <c r="F2" s="310"/>
+      <c r="C2" s="323"/>
+      <c r="D2" s="323"/>
+      <c r="E2" s="323"/>
+      <c r="F2" s="324"/>
       <c r="G2" s="210" t="s">
         <v>82</v>
       </c>
@@ -26932,11 +26664,11 @@
       <c r="CY2" s="200"/>
     </row>
     <row r="3" spans="1:103">
-      <c r="B3" s="311"/>
-      <c r="C3" s="312"/>
-      <c r="D3" s="312"/>
-      <c r="E3" s="312"/>
-      <c r="F3" s="313"/>
+      <c r="B3" s="325"/>
+      <c r="C3" s="326"/>
+      <c r="D3" s="326"/>
+      <c r="E3" s="326"/>
+      <c r="F3" s="327"/>
       <c r="G3" s="266" t="s">
         <v>87</v>
       </c>
@@ -26951,11 +26683,11 @@
       <c r="CY3" s="200"/>
     </row>
     <row r="4" spans="1:103" s="203" customFormat="1">
-      <c r="B4" s="311"/>
-      <c r="C4" s="312"/>
-      <c r="D4" s="312"/>
-      <c r="E4" s="312"/>
-      <c r="F4" s="313"/>
+      <c r="B4" s="325"/>
+      <c r="C4" s="326"/>
+      <c r="D4" s="326"/>
+      <c r="E4" s="326"/>
+      <c r="F4" s="327"/>
       <c r="G4" s="267" t="s">
         <v>141</v>
       </c>
@@ -26966,11 +26698,11 @@
       <c r="M4" s="201"/>
     </row>
     <row r="5" spans="1:103" s="203" customFormat="1">
-      <c r="B5" s="311"/>
-      <c r="C5" s="312"/>
-      <c r="D5" s="312"/>
-      <c r="E5" s="312"/>
-      <c r="F5" s="313"/>
+      <c r="B5" s="325"/>
+      <c r="C5" s="326"/>
+      <c r="D5" s="326"/>
+      <c r="E5" s="326"/>
+      <c r="F5" s="327"/>
       <c r="G5" s="267" t="s">
         <v>129</v>
       </c>
@@ -26981,11 +26713,11 @@
       <c r="M5" s="201"/>
     </row>
     <row r="6" spans="1:103" ht="15.75" thickBot="1">
-      <c r="B6" s="314"/>
-      <c r="C6" s="315"/>
-      <c r="D6" s="315"/>
-      <c r="E6" s="315"/>
-      <c r="F6" s="316"/>
+      <c r="B6" s="328"/>
+      <c r="C6" s="329"/>
+      <c r="D6" s="329"/>
+      <c r="E6" s="329"/>
+      <c r="F6" s="330"/>
       <c r="G6" s="209" t="s">
         <v>128</v>
       </c>
@@ -27014,11 +26746,11 @@
     </row>
     <row r="8" spans="1:103">
       <c r="A8" s="199"/>
-      <c r="B8" s="317" t="s">
+      <c r="B8" s="331" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="318"/>
-      <c r="D8" s="319"/>
+      <c r="C8" s="332"/>
+      <c r="D8" s="333"/>
       <c r="E8" s="202" t="s">
         <v>88</v>
       </c>
@@ -27209,13 +26941,13 @@
         <v>83</v>
       </c>
       <c r="E16" s="280" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="281" t="s">
         <v>148</v>
       </c>
-      <c r="F16" s="281" t="s">
+      <c r="G16" s="282" t="s">
         <v>149</v>
-      </c>
-      <c r="G16" s="282" t="s">
-        <v>150</v>
       </c>
       <c r="H16" s="211"/>
       <c r="J16" s="277"/>
@@ -27570,6 +27302,5 @@
   <phoneticPr fontId="16"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="55" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>